--- a/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
@@ -575,46 +575,46 @@
         <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18.93513310836146</v>
+        <v>18.87448760054221</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106051450740864</v>
+        <v>-4.092537722382808</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.64852874997968</v>
+        <v>-11.61088746219838</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.372896047499388</v>
+        <v>-4.358732372711394</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.06283870577128</v>
+        <v>-12.0240569735673</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.76812478095986</v>
+        <v>-11.73000656164891</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-19.00928324491863</v>
+        <v>-18.94812158719348</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.90446328808189</v>
+        <v>-15.8531064663833</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.39091805113127</v>
+        <v>-12.35104522866499</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-20.40459069705679</v>
+        <v>-20.33926217325092</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.45367227267529</v>
+        <v>-13.41153558884387</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.841173120401194</v>
+        <v>-9.810770362870521</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.683124165746314</v>
+        <v>-6.662702881695616</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.731823247003959</v>
+        <v>0.728304725434171</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-10.18574601251592</v>
+        <v>-10.15268451130995</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2589510461712763</v>
+        <v>-0.2577425772202488</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.193969989117697</v>
+        <v>3.183940901352827</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.372940150741321</v>
+        <v>-4.35858536189923</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.913001544126629</v>
+        <v>-4.896904872986973</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.616536988195207</v>
+        <v>-4.601118458636783</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702516208762923</v>
+        <v>-4.686968843660367</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.533984259455615</v>
+        <v>2.526183390830909</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.087947898831096</v>
+        <v>-9.058258716708046</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.477136503664816</v>
+        <v>5.459335261350482</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.418188771582869</v>
+        <v>1.41262038359347</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.309983794459868</v>
+        <v>5.291616691566333</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.03204597831089</v>
+        <v>1.027699606297546</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.000468477065553</v>
+        <v>8.970062967190785</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.493438320213222</v>
+        <v>-2.485072488841112</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.67840031541386</v>
+        <v>-7.652922774845742</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.217489463827945</v>
+        <v>6.197440933289869</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.775264170945256</v>
+        <v>2.766447851517505</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.488093132583529</v>
+        <v>-8.460091656092821</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.616617610301326</v>
+        <v>-4.600989463271063</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.451035886168718</v>
+        <v>2.443410855112084</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-8.74955536160774</v>
+        <v>-8.720578566626223</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.922964197145184</v>
+        <v>1.917064080449173</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.507799135770327</v>
+        <v>-2.49974096239157</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.02827430832383</v>
+        <v>8.001023293999907</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.9023994661721417</v>
+        <v>0.8981904655438342</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.063224602103809</v>
+        <v>4.048910911459323</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.851045664838438</v>
+        <v>-2.843123845996033</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.125017267577199</v>
+        <v>-5.107826183303843</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.473850475644014</v>
+        <v>-1.468423107768963</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.869271619533926</v>
+        <v>-1.862967093186768</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.161335788921598</v>
+        <v>6.141196593608264</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18.79510731484768</v>
+        <v>18.73353440485458</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.46267041079074</v>
+        <v>16.40899180824617</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.204121674500584</v>
+        <v>3.193883450427819</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.009288667018836</v>
+        <v>7.983441267052719</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.676435011403548</v>
+        <v>2.667949332815034</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8122893118616261</v>
+        <v>-0.8096918615755584</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.621382825163991</v>
+        <v>1.614820062256037</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.656444576107226</v>
+        <v>1.649676453755717</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.874902345988616</v>
+        <v>3.860970347586942</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.486445022413371</v>
+        <v>1.480184424681866</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.61466978789813</v>
+        <v>6.271028035868859</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.30068174523123</v>
+        <v>1.434117201578673</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.37031974450672</v>
+        <v>11.60516912380788</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.093785505450441</v>
+        <v>5.703790802699849</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.592192568751194</v>
+        <v>2.907603963394678</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.978408039691217</v>
+        <v>5.569702563240966</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.284984450800415</v>
+        <v>4.789536915009201</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.642185872911867</v>
+        <v>9.664975936630832</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.274020530605831</v>
+        <v>5.896008712865999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.232262194737956</v>
+        <v>5.86100267072802</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.417821140099647</v>
+        <v>4.993172759155179</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.553815145253637</v>
+        <v>7.388301812607452</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.12503503960788</v>
+        <v>2.425906552601077</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.344249705563804</v>
+        <v>2.676356673483802</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.031072728812127</v>
+        <v>-3.204951903650951</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.983827133868779</v>
+        <v>-3.162747675692202</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.943710856968025</v>
+        <v>-5.216763420464417</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.307077043033011</v>
+        <v>-5.603091091740843</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.526882353480872</v>
+        <v>-1.608415936584997</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.689406002708431</v>
+        <v>-8.123270971704962</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-8.845232195326055</v>
+        <v>-9.347310748013712</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-12.52485775177377</v>
+        <v>-13.23300080844085</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.281441295651717</v>
+        <v>-8.750900087306775</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.18261251510349</v>
+        <v>-10.75445496020222</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.24183981524272</v>
+        <v>-8.682950104584506</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.286066548588266</v>
+        <v>-9.782576645464033</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-10.15980251404716</v>
+        <v>-10.71233007048505</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.39666841274447</v>
+        <v>-10.96000696287915</v>
       </c>
     </row>
     <row r="12">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.2079</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4046</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.1303606450524057</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1909</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4018~4031</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4018</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.0002604487140658307</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1739</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3992~4005</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3992</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.0658625536976345</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1568</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3964~3977</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3964</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.08388126741889579</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1398</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3926~3939</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3926</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1341321291426496</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1228</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3860~3865</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3860</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.02920074835406439</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1058</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3772~3772</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3772</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.1046528780933116</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.08872</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3651~3651</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3651</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.2866219372537344</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.0717</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3494~3494</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3494</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.5975748452164709</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.05467</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3313~3313</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3313</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.8117231648488854</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03764</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3079~3079</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3079</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.7056522936256897</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02061</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2759~2759</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2759</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.076695786350378</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.003583</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2412~2412</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2412</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.362283072824852</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.01345</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2109~2109</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2109</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.987358265849771</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.03047</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1823~1823</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1823</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.922359814732431</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.0475</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1557~1557</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1557</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.548308629051434</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.06453</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1306~1306</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1306</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.56016045467517</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.08156</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1075~1075</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1075</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.948422144906303</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.09859</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>937~937</t>
-        </is>
+      <c r="B24" t="n">
+        <v>937</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.002826354283094</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.1156</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>777~777</t>
-        </is>
+      <c r="B25" t="n">
+        <v>777</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.491117664346007</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1326</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>629~629</t>
-        </is>
+      <c r="B26" t="n">
+        <v>629</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.514510805386216</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.1497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>529~529</t>
-        </is>
+      <c r="B27" t="n">
+        <v>529</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.894085309279625</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.1667</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>435~435</t>
-        </is>
+      <c r="B28" t="n">
+        <v>435</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.449090415422205</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1837</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>359~359</t>
-        </is>
+      <c r="B29" t="n">
+        <v>359</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.938316554441833</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.2008</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>282~282</t>
-        </is>
+      <c r="B30" t="n">
+        <v>282</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.761880828726191</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.2178</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>234~234</t>
-        </is>
+      <c r="B31" t="n">
+        <v>234</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.352715525943871</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.2348</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>189~189</t>
-        </is>
+      <c r="B32" t="n">
+        <v>189</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.474815648043993</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.2518</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>144~144</t>
-        </is>
+      <c r="B33" t="n">
+        <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.798993875765532</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.2689</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>101~101</t>
-        </is>
+      <c r="B34" t="n">
+        <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.952106234245477</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.2859</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.723429149669542</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.2079</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-3.095847958764196</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1909</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>111~111</t>
-        </is>
+      <c r="B7" t="n">
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.461516634744982</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1739</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>137~137</t>
-        </is>
+      <c r="B8" t="n">
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.06130620533747333</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1568</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>165~165</t>
-        </is>
+      <c r="B9" t="n">
+        <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3722261989978506</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1398</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>203~203</t>
-        </is>
+      <c r="B10" t="n">
+        <v>203</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.261911226613911</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1228</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>269~277</t>
-        </is>
+      <c r="B11" t="n">
+        <v>269</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.5751537375517586</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1058</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>357~370</t>
-        </is>
+      <c r="B12" t="n">
+        <v>357</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3312761580478139</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.08872</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>478~491</t>
-        </is>
+      <c r="B13" t="n">
+        <v>478</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.576941375199794</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.0717</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>635~648</t>
-        </is>
+      <c r="B14" t="n">
+        <v>635</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.802080295518621</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.05467</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>816~829</t>
-        </is>
+      <c r="B15" t="n">
+        <v>816</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-2.915633736374026</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03764</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1050~1063</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1050</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.787887990953152</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02061</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1370~1383</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1370</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.95113897096919</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.003583</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1717~1730</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1717</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.741993233504772</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.01345</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2020~2033</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2020</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.927771817504613</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.03047</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2306~2319</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2306</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.393826418528214</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.0475</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2572~2585</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2572</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.429608532975934</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.06453</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2823~2836</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2823</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.083001084666961</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.08156</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3054~3067</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3054</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.9446936185471131</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.09859</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3192~3205</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3192</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.7929703014892269</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.1156</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3352~3365</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3352</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.7252362399722259</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1326</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3500~3513</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3500</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.372743757158446</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.1497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3600~3613</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3600</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.3484064907054147</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.1667</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3694~3707</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3694</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2139670496407859</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1837</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3770~3783</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3770</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.2068932501597445</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.2008</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3847~3860</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3847</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.05820515958821204</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.2178</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3895~3908</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3895</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.01135029564497358</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.2348</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3940~3953</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3940</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.001659924055154249</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.2518</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3985~3998</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3985</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.132874836368309</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.2689</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4028~4041</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4028</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.006430153914507741</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.2859</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4046</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.03181420504255783</v>

--- a/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-14-50 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-14-50 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18.87448760054221</v>
+        <v>18.8869831406274</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092537722382808</v>
+        <v>-4.079670750552907</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.61088746219838</v>
+        <v>-11.59792490786734</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.358732372711394</v>
+        <v>-4.345789208510375</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.0240569735673</v>
+        <v>-12.0109830617032</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.73000656164891</v>
+        <v>-11.71699626994054</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-18.94812158719348</v>
+        <v>-18.93508695194567</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.8531064663833</v>
+        <v>-15.83995164210154</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.35104522866499</v>
+        <v>-12.33786722668477</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-20.33926217325092</v>
+        <v>-20.32587576867202</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.41153558884387</v>
+        <v>-13.39809100624947</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.810770362870521</v>
+        <v>-9.797326095676056</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.662702881695616</v>
+        <v>-6.649150686654551</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.728304725434171</v>
+        <v>0.7178750897327646</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-10.15268451130995</v>
+        <v>-10.14021272346846</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2577425772202488</v>
+        <v>-0.2448733468473918</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.183940901352827</v>
+        <v>3.196912928534687</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.35858536189923</v>
+        <v>-4.345642719768904</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.896904872986973</v>
+        <v>-4.883827534620451</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.601118458636783</v>
+        <v>-4.588105115596186</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.686968843660367</v>
+        <v>-4.673928494885772</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.526183390830909</v>
+        <v>2.539344689123212</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.058258716708046</v>
+        <v>-9.045080015131887</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.459335261350482</v>
+        <v>5.472727812372405</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.41262038359347</v>
+        <v>1.426067549387575</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.291616691566333</v>
+        <v>5.305062728451347</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.027699606297546</v>
+        <v>1.041252226288769</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.970062967190785</v>
+        <v>8.959633331494381</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.485072488841112</v>
+        <v>-2.472595178479331</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.652922774845742</v>
+        <v>-7.640059728409589</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.197440933289869</v>
+        <v>6.210414615996704</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.766447851517505</v>
+        <v>2.779394481807707</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.460091656092821</v>
+        <v>-8.447016846403159</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.600989463271063</v>
+        <v>-4.587976554376397</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.443410855112084</v>
+        <v>2.456453993048825</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-8.720578566626223</v>
+        <v>-8.707421810944759</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.917064080449173</v>
+        <v>1.930245957386774</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.49974096239157</v>
+        <v>-2.486350587200803</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.001023293999907</v>
+        <v>8.014471582971979</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.8981904655438342</v>
+        <v>0.9116358682505492</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.048910911459323</v>
+        <v>4.062463678117808</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481692565</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.107826183303843</v>
+        <v>-5.095351866315639</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.468423107768963</v>
+        <v>-1.455556146252242</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.862967093186768</v>
+        <v>-1.849999633523581</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.141196593608264</v>
+        <v>6.154144891180827</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18.73353440485458</v>
+        <v>18.7466243663191</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.40899180824617</v>
+        <v>16.42201505288149</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.193883450427819</v>
+        <v>3.206926558224559</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.983441267052719</v>
+        <v>7.996604049364485</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.667949332815034</v>
+        <v>2.681131179627769</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8096918615755584</v>
+        <v>-0.7963013066438407</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.614820062256037</v>
+        <v>1.628266985193235</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.649676453755717</v>
+        <v>1.663121840999075</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.860970347586942</v>
+        <v>3.874523051665186</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.480184424681866</v>
+        <v>1.469754788980111</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>66</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.271028035868859</v>
+        <v>6.285152073278169</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.434117201578673</v>
+        <v>1.44868202746153</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.60516912380788</v>
+        <v>11.61984585923545</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.703790802699849</v>
+        <v>5.718436631379667</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.907603963394678</v>
+        <v>2.092067793406095</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.569702563240966</v>
+        <v>4.757804320042602</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.789536915009201</v>
+        <v>3.975493471923876</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>9.664975936630832</v>
+        <v>8.844570960667255</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.896008712865999</v>
+        <v>5.073840304882026</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.86100267072802</v>
+        <v>5.027461986680606</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.993172759155179</v>
+        <v>4.161820388320876</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.388301812607452</v>
+        <v>6.558297875855565</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.425906552601077</v>
+        <v>2.439459077883896</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.676356673483802</v>
+        <v>2.665927037787029</v>
       </c>
     </row>
     <row r="11">
@@ -832,153 +832,153 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.204951903650951</v>
+        <v>-3.154636433702038</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.162747675692202</v>
+        <v>-3.721591781577054</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.216763420464417</v>
+        <v>-5.757024949487409</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.603091091740843</v>
+        <v>-6.137734846424621</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.608415936584997</v>
+        <v>-1.578265529449077</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.123270971704962</v>
+        <v>-8.019555171777924</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.347310748013712</v>
+        <v>-9.229315717533261</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-13.23300080844085</v>
+        <v>-13.07182585696555</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.750900087306775</v>
+        <v>-8.639589735713677</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.75445496020222</v>
+        <v>-10.62154118671987</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.682950104584506</v>
+        <v>-8.577305716696934</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.782576645464033</v>
+        <v>-9.66535932526233</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-10.71233007048505</v>
+        <v>-11.2149244076831</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.96000696287915</v>
+        <v>-10.35756632278567</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09726</t>
+          <t>X ≈ -0.09727</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.386000303681051</v>
+        <v>-5.80805777056176</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.997573916645678</v>
+        <v>-6.984664107069626</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.08665749927458</v>
+        <v>-4.073650367856978</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.477065523692438</v>
+        <v>-1.464086381293974</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.015486738764416</v>
+        <v>-2.002375934389477</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.718044801048755</v>
+        <v>-1.70500190475439</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.935009923280084</v>
+        <v>-5.921943668979608</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.402193322061407</v>
+        <v>-6.38901231276617</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.810300646260046</v>
+        <v>-4.797101907305283</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.833979550296242</v>
+        <v>-4.820574422643411</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.691625436597285</v>
+        <v>-6.678168142887067</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.136581122227064</v>
+        <v>-9.123128833506954</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.38328201416295</v>
+        <v>-10.36972596781135</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-10.96000696287915</v>
+        <v>-10.9704365985773</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08021</t>
+          <t>X ≈ -0.08022</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>157</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.633565708745003</v>
+        <v>-6.62104341906938</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.519024672027733</v>
+        <v>-9.506114862451682</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.729180002828144</v>
+        <v>-6.716172871410542</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-9.146697570857448</v>
+        <v>-9.133718428458984</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.048176110770669</v>
+        <v>-9.03506530639573</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.292135446940215</v>
+        <v>-4.279092550645849</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.08172956190201575</v>
+        <v>0.09479581620249178</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.933224537516139</v>
+        <v>-2.920043528220901</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.631167098857965</v>
+        <v>-3.617968359903202</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.755177634204223</v>
+        <v>-5.741772506551392</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.596873633681327</v>
+        <v>-6.583416339971109</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.83637582665451</v>
+        <v>-7.8229235379344</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-10.16745846307698</v>
+        <v>-10.15390241672537</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-11.19162248111887</v>
+        <v>-11.20205211681702</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>181</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.322167601977931</v>
+        <v>-3.309645312302308</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.828768839251573</v>
+        <v>-3.815859029675522</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.881096109384082</v>
+        <v>-5.86808897796648</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.093384413240798</v>
+        <v>-4.080405270842334</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7644023133955855</v>
+        <v>-0.7512915090206462</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.571932751370781</v>
+        <v>-1.558889855076416</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.209152656488122</v>
+        <v>-2.196086402187646</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.438766994496262</v>
+        <v>-5.425585985201025</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.737335941451924</v>
+        <v>-2.724137202497161</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.139947314325156</v>
+        <v>-4.126542186672324</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.344700638642735</v>
+        <v>-4.331243344932517</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.205345105606561</v>
+        <v>-3.191892816886451</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.625599716551719</v>
+        <v>-3.612043670200116</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6134474450489122</v>
+        <v>-0.6238770807470644</v>
       </c>
     </row>
     <row r="15">
@@ -1043,98 +1043,98 @@
         <v>234</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.20741638064473</v>
+        <v>2.219938670320353</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.619777479887389</v>
+        <v>3.632784611304992</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.784258970072109</v>
+        <v>2.797369774447048</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.791102617189672</v>
+        <v>4.804145513484038</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8602150537635467</v>
+        <v>0.8732813080640227</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.957134219084516</v>
+        <v>2.970315228379754</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9500195132516396</v>
+        <v>-0.9368207742968764</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3366074384724698</v>
+        <v>0.3500125661253009</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9865549688557564</v>
+        <v>1.000012262565974</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.448288553551613</v>
+        <v>1.461740842271723</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.882734797307663</v>
+        <v>1.896290843659266</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.559806556934376</v>
+        <v>2.549376921236224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02912</t>
+          <t>X ≈ -0.02914</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.637655842446577</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9800119331742323</v>
+        <v>-0.8005660734414377</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.937380639770964</v>
+        <v>-2.762735577318814</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.494627507163315</v>
+        <v>-2.319030809905854</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.470548722235421</v>
+        <v>-1.28992224387936</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.673106784519831</v>
+        <v>-3.500385204839887</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.820340501792181</v>
+        <v>-2.644656692632772</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.725023900573603</v>
+        <v>-1.857806841121629</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.161023786755841</v>
+        <v>-1.2918297499955</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.698648971783847</v>
+        <v>-1.828268922500911</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.903402296101426</v>
+        <v>-2.032970080761103</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.556519138755988</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.664273749700882</v>
+        <v>-1.791783534070291</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.727052417424602</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="17">
@@ -1147,358 +1147,358 @@
         <v>347</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.908423910988077</v>
+        <v>-0.6077171832721078</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.820060112935337</v>
+        <v>3.544785484470985</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.0330218501453956</v>
+        <v>-0.308199156768211</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.09723128246210422</v>
+        <v>-0.1779740131798491</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.32303431301353</v>
+        <v>-3.59810794667893</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.008301309015515</v>
+        <v>-1.283442850761418</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.245772778449172</v>
+        <v>-2.520890962189036</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4074806729079086</v>
+        <v>-0.3942996636126708</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6842571930711117</v>
+        <v>0.6974559320258749</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1658679919567447</v>
+        <v>-0.1524628643039136</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4939319978467012</v>
+        <v>0.5073892915569189</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.200791473049939</v>
+        <v>-1.187339184329829</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.26079829640868</v>
+        <v>1.274354342760283</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.222335190644564</v>
+        <v>1.211905554946412</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.004934</t>
+          <t>X ≈ 0.004925</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.988487825160469</v>
+        <v>-3.138810767376462</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.949896421623222</v>
+        <v>-2.776312649914047</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.684699121619005</v>
+        <v>-2.513189297826905</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.554445989011505</v>
+        <v>-2.382964154238543</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7826361809814415</v>
+        <v>-0.6186221283868676</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.504904766635363</v>
+        <v>0.6655940065113839</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.070336065864652</v>
+        <v>2.225620489350469</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.9430866604824999</v>
+        <v>1.100657108721627</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4380452389011964</v>
+        <v>-0.2761145214853613</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.2980714140280654</v>
+        <v>-0.1391912125520562</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.492923748246639</v>
+        <v>-1.330734476075413</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1384085776998774</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.538861208446917</v>
+        <v>-2.374401913875744</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.289139876170474</v>
+        <v>-2.148666263649069</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.02196</t>
+          <t>X ≈ 0.02195</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.401666574894918</v>
+        <v>2.255926074728812</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.839044010881793</v>
+        <v>2.048248753594841</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3040764439666219</v>
+        <v>-0.1009085960725926</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.973029835493946</v>
+        <v>3.18721128435795</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.483559669372902</v>
+        <v>3.701553310209626</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.032749858836738</v>
+        <v>2.244541374932354</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.248715442263837</v>
+        <v>1.458076629701345</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.480832742782958</v>
+        <v>1.692762371879596</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.119133555901506</v>
+        <v>2.333534601321659</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.618658720523847</v>
+        <v>1.4836158049918</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.113206095506975</v>
+        <v>1.980669032696525</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.846889952153106</v>
+        <v>2.716801571016745</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.776285690858629</v>
+        <v>2.647527910685795</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.725307722435531</v>
+        <v>3.925895139859698</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.03898</t>
+          <t>X ≈ 0.03897</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>266</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.741558620961897</v>
+        <v>-1.729036331286224</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.232831482046414</v>
+        <v>-5.219921672470321</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.627700188643004</v>
+        <v>-5.990632906849378</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.256845552276019</v>
+        <v>-9.619806259501658</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-10.54714646659644</v>
+        <v>-10.90997551184552</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-10.24970452888073</v>
+        <v>-10.61260148221043</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.078799148408656</v>
+        <v>-8.441672743732191</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.170042697566011</v>
+        <v>-8.532801537894997</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.23104258374839</v>
+        <v>-8.59378369441756</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.193949723663494</v>
+        <v>-4.180544596010705</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.774642897605176</v>
+        <v>-4.761185603894958</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.236500341763509</v>
+        <v>-3.223048053043399</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.40111585496404</v>
+        <v>-1.387559808612359</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.02357497381562013</v>
+        <v>-0.4099444591378401</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.05602</t>
+          <t>X ≈ 0.056</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.486641361064969</v>
+        <v>2.677814128195813</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.859131493120593</v>
+        <v>4.638056606560554</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.464262786524003</v>
+        <v>4.640110618630906</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.008858548613567</v>
+        <v>1.198907190790656</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.462469206051409</v>
+        <v>2.644744621821985</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.955130267272999</v>
+        <v>4.132594841933269</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.065615673506699</v>
+        <v>5.238360673143241</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.606400402215236</v>
+        <v>2.787165045229571</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.139026014040951</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.687307203514926</v>
+        <v>3.860391076503909</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.482553879197432</v>
+        <v>3.655689918243759</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.516937036542821</v>
+        <v>3.69006807059904</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.495088800099907</v>
+        <v>3.66674261411103</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6376599871456676</v>
+        <v>-0.4726011007417554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.07304</t>
+          <t>X ≈ 0.07303</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>231</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7533149265432684</v>
+        <v>0.7658372162188911</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.73914391098161</v>
+        <v>1.752053720557662</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.210076070185892</v>
+        <v>2.223083201603494</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.041627904092088</v>
+        <v>1.054607046490553</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5032066890198763</v>
+        <v>0.5163174933948156</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.229654403567402</v>
+        <v>-2.216611507273036</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.344691151142761</v>
+        <v>-5.331624896842285</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.21447195252167</v>
+        <v>-3.201290943226432</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.007073570305742</v>
+        <v>-4.993874831350979</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.290099188234052</v>
+        <v>-6.276694060581221</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.92775294545212</v>
+        <v>-6.914295651741902</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.027568922305775</v>
+        <v>-6.014116633585665</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-8.179425264852405</v>
+        <v>-8.165869218500802</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.496803499675686</v>
+        <v>-7.507233135373838</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.09007</t>
+          <t>X ≈ 0.09006</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.579025447905892</v>
+        <v>2.591547737581514</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.255723963358335</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.645046896461061</v>
+        <v>5.658054027878663</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.49993771022806</v>
+        <v>6.512916852626525</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.236878813996469</v>
+        <v>5.249989618371409</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.08504538939313</v>
+        <v>4.098088285687496</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.623500077918109</v>
+        <v>7.636566332218585</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.257765954498943</v>
+        <v>4.270946963794181</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.819954474113658</v>
+        <v>7.833153213068421</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.795916245607472</v>
+        <v>4.809321373260303</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.692612196652284</v>
+        <v>1.706069490362502</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.726995353997715</v>
+        <v>1.740447642717825</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.306740743052735</v>
+        <v>1.320296789404338</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.556462075329023</v>
+        <v>1.546032439630871</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>160</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6315616797900887</v>
+        <v>0.6440839694657114</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.230011933174225</v>
+        <v>-2.217102123598174</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.374880639770858</v>
+        <v>-1.361873508353256</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.880372492836614</v>
+        <v>1.893351635235078</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.216951277764544</v>
+        <v>3.230062082139483</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.639393215480176</v>
+        <v>6.652436111774541</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10.92965949820782</v>
+        <v>10.9427257525083</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>11.71247609942632</v>
+        <v>11.72565710872156</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.526476213244131</v>
+        <v>8.539674952198894</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.676351028216153</v>
+        <v>7.689756155868984</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.221597703898517</v>
+        <v>6.235054997608735</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.380980861243941</v>
+        <v>4.394433149964051</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.960726250299103</v>
+        <v>3.974282296650706</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.210447582575391</v>
+        <v>4.200017946877239</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>148</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7.641696814925126</v>
+        <v>7.654219104600749</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.732825904663606</v>
+        <v>8.745735714239657</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>8.337957198067052</v>
+        <v>8.350964329484654</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.143886006350186</v>
+        <v>9.156865148748651</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.551410737223925</v>
+        <v>4.564521541598864</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.146149972236927</v>
+        <v>2.159192868531292</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.737091930640325</v>
+        <v>2.750158184940801</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.945584207534495</v>
+        <v>2.958765216829732</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.20890864567648</v>
+        <v>2.222107384631244</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.007432109297248246</v>
+        <v>0.02083723695007933</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.927050944750071</v>
+        <v>-4.913593651039854</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.89266778740464</v>
+        <v>-4.87921549868453</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.38752539039757</v>
+        <v>-4.397955026095723</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>100</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5065616797900816</v>
+        <v>0.5190839694657043</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.894988066825768</v>
+        <v>8.907897876401819</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>9.500119360229178</v>
+        <v>9.51312649164678</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.630372492836678</v>
+        <v>6.643351635235142</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>9.091951277764508</v>
+        <v>9.105062082139447</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10.38939321548017</v>
+        <v>10.40243611177453</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.304659498207897</v>
+        <v>1.317725752508373</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1625239005736745</v>
+        <v>-0.1493428912784367</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.776476213244081</v>
+        <v>2.789674952198844</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.926351028216217</v>
+        <v>3.939756155869048</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.721597703898581</v>
+        <v>2.735054997608799</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.335726250299111</v>
+        <v>2.349282296650713</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>94</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.95337019042833</v>
+        <v>4.965892480103953</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1503072157619343</v>
+        <v>0.1632170253379854</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.308391278068697</v>
+        <v>-1.295384146651095</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.141010790709018</v>
+        <v>4.153989933107482</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.794078937338973</v>
+        <v>6.807189741713913</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.0276910878206</v>
+        <v>6.040733984114965</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.006787157782355</v>
+        <v>7.019853412082831</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.667263333469002</v>
+        <v>8.68044434276424</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.287114511116393</v>
+        <v>3.300313250071156</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.756138262258652</v>
+        <v>7.769543389911483</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.615214725175179</v>
+        <v>8.628672018885396</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.713427669754651</v>
+        <v>9.726879958474761</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.42083263327783</v>
+        <v>11.43438867962944</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.351405029383969</v>
+        <v>6.340975393685817</v>
       </c>
     </row>
     <row r="28">
@@ -1719,150 +1719,150 @@
         <v>76</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.473935435246815</v>
+        <v>2.486845244822867</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7632772549660274</v>
+        <v>0.7762843863836295</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.209319861257725</v>
+        <v>2.22229900365619</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-7.539627669603874</v>
+        <v>-7.526516865228935</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.294817310835619</v>
+        <v>-3.281774414541253</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.363791888900103</v>
+        <v>5.376972898195341</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.618581476402021</v>
+        <v>6.631780215356784</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.452666817689845</v>
+        <v>4.466071945342676</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.932124019688047</v>
+        <v>2.945581313398264</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.75677888187806</v>
+        <v>11.77033492822966</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.32228968783843</v>
+        <v>13.31186005214028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1923</t>
+          <t>X ≈ 0.1922</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>77</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.246821420049805</v>
+        <v>7.259343709725428</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.232650404488105</v>
+        <v>8.245560214064156</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.240379100488916</v>
+        <v>5.253386231906518</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.669333531797712</v>
+        <v>6.682312674196176</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.02701621282941</v>
+        <v>10.04012701720435</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.727055553142471</v>
+        <v>7.740098449436836</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.746217939766332</v>
+        <v>3.759284194066808</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.577735839686092</v>
+        <v>4.59091684898133</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.516735953503868</v>
+        <v>4.529934692458632</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.562714664579794</v>
+        <v>7.576119792232625</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.25406523636612</v>
+        <v>11.26752253007633</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.691045796308913</v>
+        <v>8.704498085029023</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.06299897757184</v>
+        <v>16.07655502392345</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.71531771244557</v>
+        <v>13.70488807674742</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.2093</t>
+          <t>X ≈ 0.2092</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.756561679789968</v>
+        <v>3.769083969465591</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.061654733492432</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.916786026895785</v>
+        <v>5.929793158313387</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>18.54703915950328</v>
+        <v>18.56001830190174</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.675284611097851</v>
+        <v>9.68839541547279</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.639393215480226</v>
+        <v>1.652436111774591</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.254142766093054</v>
+        <v>5.267323775388292</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.10980954657736</v>
+        <v>3.123008285532123</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.426351028216217</v>
+        <v>6.439756155869048</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>14.55493103723198</v>
+        <v>14.5683883309422</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.16905958363245</v>
+        <v>14.18261562998406</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>45</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.33943251127021</v>
+        <v>10.35234232084626</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.055674915784792</v>
+        <v>1.068682047202394</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.702960840496594</v>
+        <v>-7.68998169809813</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.796937611124385</v>
+        <v>-3.783826806749445</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9449487710356905</v>
+        <v>0.9579916673300559</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.749103942652333</v>
+        <v>9.762170196952809</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.059698321648611</v>
+        <v>7.072879330943849</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.220920657688531</v>
+        <v>9.234119396643294</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.59301769488276</v>
+        <v>10.60642282253559</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.61048659278741</v>
+        <v>12.62394388649763</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.200425305688483</v>
+        <v>8.213877594408594</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>45</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>11.95100612423447</v>
+        <v>11.96352841391009</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.117210289047989</v>
+        <v>8.13012009862404</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.07481693728112</v>
+        <v>10.08779607967958</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.536395722208951</v>
+        <v>9.54950652658389</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.167170993257976</v>
+        <v>3.180213889552341</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.554253991021859</v>
+        <v>2.567452729976623</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.943819926120803</v>
+        <v>5.95727721983102</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.64486975013294</v>
+        <v>12.65832203885305</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.66905958363244</v>
+        <v>16.68261562998404</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>16.9187809159087</v>
+        <v>16.90835128021055</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>43</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-12.95855459927976</v>
+        <v>-12.94603230960414</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-19.22129100294168</v>
+        <v>-19.20838119336562</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.31383412814291</v>
+        <v>-10.30082699672531</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.85799960018656</v>
+        <v>-7.845020457788095</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-10.72200221060758</v>
+        <v>-10.70889140623265</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.773397482194255</v>
+        <v>-5.76035458589989</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.183712594815383</v>
+        <v>-8.170646340514907</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.9764773889457</v>
+        <v>-10.96329637965047</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-8.711895879779185</v>
+        <v>-8.698697140824422</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.585276878760602</v>
+        <v>-2.571871751107771</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4644488077293261</v>
+        <v>-0.4509915140191083</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.081228441081592</v>
+        <v>-5.067776152361482</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.475261134020045</v>
+        <v>1.488817180371647</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.050563861645195</v>
+        <v>4.040134225947043</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.2774</t>
+          <t>X ≈ 0.2773</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.617672790901175</v>
+        <v>8.630195080576797</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.5616547334924</v>
+        <v>12.57456454306845</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.055674915784692</v>
+        <v>1.068682047202294</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>1.198907190790699</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.203062388875622</v>
+        <v>6.216173193250562</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.500504326591283</v>
+        <v>6.513547222885649</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.41577060931904</v>
+        <v>6.428836863619516</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>5.961768219832742</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.887587324355238</v>
+        <v>5.900786063310001</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.073648971783797</v>
+        <v>-6.060243844130966</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.7995746943115</v>
+        <v>-11.78612240559139</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.21982930525649</v>
+        <v>-12.20627325890489</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.9701079729802</v>
+        <v>-11.98053760867835</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-14-50 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-14-50 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1303606450524057</v>
+        <v>0.1299214078892916</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.08424385785583155</v>
+        <v>0.08380327181940572</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02316594637657232</v>
+        <v>0.02273713728502003</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01893265062759752</v>
+        <v>0.01850568995537571</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.03751851261773709</v>
+        <v>-0.0379359454739685</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.05145537630897223</v>
+        <v>0.05101810930844408</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.04446460739290359</v>
+        <v>-0.04487908222277071</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.02010196319736224</v>
+        <v>0.01966771814674217</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02727594671642208</v>
+        <v>-0.02769918403017613</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1477230458579157</v>
+        <v>-0.1481233800480695</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3880590014607677</v>
+        <v>-0.3884017925146637</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.413979613064285</v>
+        <v>-0.4143159238812686</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3509552421644386</v>
+        <v>-0.3513105887247718</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3591890956252897</v>
+        <v>-0.3587601603626851</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0002604487140658307</v>
+        <v>-0.0007573003756178309</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1133503497041772</v>
+        <v>0.1128098089247658</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1042394892934624</v>
+        <v>0.1036972112497594</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.04943902709685233</v>
+        <v>0.04891132746646321</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04601137212755191</v>
+        <v>0.04547916257639173</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1335561563644276</v>
+        <v>0.1330047733091746</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08726819386006213</v>
+        <v>0.08672724282132549</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1307166560864275</v>
+        <v>0.1301602143116938</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05860397859333233</v>
+        <v>0.05806461422668008</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.007015456119994212</v>
+        <v>-0.007546851836707447</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2973030670539174</v>
+        <v>-0.2977644951808571</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3484967506962846</v>
+        <v>-0.3489453628436294</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3069709380562031</v>
+        <v>-0.3074341212597318</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3667674497790046</v>
+        <v>-0.366260978228496</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3992</v>
+        <v>3993</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0658625536976345</v>
+        <v>0.06526469837228888</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1157672876049958</v>
+        <v>0.1151388252158014</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.08418131376402016</v>
+        <v>0.08355606207634736</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07814860478070074</v>
+        <v>0.07752600445822821</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.07820471440535215</v>
+        <v>0.07757582526788553</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1643932154801675</v>
+        <v>0.1637457843563936</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1183629240643569</v>
+        <v>0.1177257525083704</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1151149188360918</v>
+        <v>0.1144730627101183</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1179823428412803</v>
+        <v>0.1173387841148141</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.04261794075280534</v>
+        <v>-0.0432310845613344</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3084398430350817</v>
+        <v>-0.3089890464352436</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3852309564825731</v>
+        <v>-0.3857608425264942</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3156636820825582</v>
+        <v>-0.3162159507203484</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.427578469528811</v>
+        <v>-0.4269855592584904</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.08388126741889579</v>
+        <v>0.0831865335682167</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1706419903670096</v>
+        <v>0.1699044139929669</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04099986337382688</v>
+        <v>0.04028946951398638</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0591596090923403</v>
+        <v>0.0584459748577828</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1385155868508434</v>
+        <v>0.1377747142481525</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1980538398507647</v>
+        <v>0.1973014528266361</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1019397802527138</v>
+        <v>0.1012101432435131</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1775264772601375</v>
+        <v>0.1767714376060425</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1052743991851273</v>
+        <v>0.1045364131560262</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02526187500965449</v>
+        <v>-0.02597828605593122</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3671343354258454</v>
+        <v>-0.3677675830363611</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3942964962950697</v>
+        <v>-0.3949227865118061</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3464931696252265</v>
+        <v>-0.3471372696629587</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.410516090482119</v>
+        <v>-0.4098496445477267</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1341321291426496</v>
+        <v>0.1332971674351882</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.186506604154367</v>
+        <v>0.1856333422561036</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.05942847884741553</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.0002911920236670085</v>
+        <v>-0.0005396525474381519</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.04146676543752648</v>
+        <v>-0.04229564143778219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.04114715549034287</v>
+        <v>0.04030142308329943</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.07201266373039061</v>
+        <v>0.07115737426738633</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1019725388973995</v>
+        <v>0.101102061683747</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.08047010792737552</v>
+        <v>0.07960374161898898</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.01766932801793075</v>
+        <v>-0.01852417992343192</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3863177962286812</v>
+        <v>-0.3870824069713521</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4140802385523159</v>
+        <v>-0.4148376568569461</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3872174726446076</v>
+        <v>-0.3879885791130349</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4288162992381572</v>
+        <v>-0.4280378208843985</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.02920074835406439</v>
+        <v>0.02813725451479598</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1651744022294892</v>
+        <v>0.1640427664406232</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.137985739434292</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.09722978577544694</v>
+        <v>-0.09829993090516354</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.0918912908527858</v>
+        <v>-0.07878048647784652</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.05338254837275969</v>
+        <v>-0.04033965207839429</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.008649668027224777</v>
+        <v>0.004416586273251255</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.06153995443172278</v>
+        <v>-0.04835894513648498</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.01896656251976481</v>
+        <v>-0.005767823565001606</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1181854813643639</v>
+        <v>-0.1047803537115328</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.4782987228233253</v>
+        <v>-0.4648414291131076</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5474888435721468</v>
+        <v>-0.5340365548520367</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4353175207446611</v>
+        <v>-0.4363210176941905</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4819099303779666</v>
+        <v>-0.4809261090668073</v>
       </c>
     </row>
     <row r="12">
@@ -2529,98 +2529,98 @@
         <v>3772</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1046528780933116</v>
+        <v>0.1032345127998653</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.255723963358335</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.01949887943147388</v>
+        <v>-0.006491748013871756</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.0312208491463295</v>
+        <v>0.0441999915447937</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.05651107642425046</v>
+        <v>-0.04340027204931118</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1348863225851531</v>
+        <v>0.1479292188795185</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2092194133722529</v>
+        <v>0.2222856676727289</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2457475734454775</v>
+        <v>0.2589285827407153</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1847476872631759</v>
+        <v>0.1979464262179391</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1299565425321703</v>
+        <v>0.1433616701850013</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2868858591979233</v>
+        <v>-0.2734285654877056</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3320361058821888</v>
+        <v>-0.3185838171620787</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1955568886192296</v>
+        <v>-0.1820008422676267</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.237458037785153</v>
+        <v>-0.2478876734833051</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.08872</t>
+          <t>X &gt; -0.08873</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3651</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2866219372537344</v>
+        <v>0.2991442269293572</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.482772235546669</v>
+        <v>0.4956820451227202</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1152932851812452</v>
+        <v>0.1283004165988473</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.08120788040173466</v>
+        <v>0.09418702280019886</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.008412521259437256</v>
+        <v>0.02152332563437653</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1962954340504197</v>
+        <v>0.2093383303447851</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4128490353210097</v>
+        <v>0.4259152896214857</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4660710049317345</v>
+        <v>0.4792520142269723</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3502916062870938</v>
+        <v>0.363490345241857</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2944693519630803</v>
+        <v>0.3078744796159114</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.0746225097415234</v>
+        <v>-0.06116521603130565</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.04023935239609244</v>
+        <v>-0.02678706367598238</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1420806737447364</v>
+        <v>0.1556367200963393</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1179044437093353</v>
+        <v>0.1074748080111831</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3494</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5975748452164709</v>
+        <v>0.6100971348920936</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9321947067799741</v>
+        <v>0.9451045163560252</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4228440310935184</v>
+        <v>0.4358511625111205</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4958561791560854</v>
+        <v>0.5088353215545496</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4153628404433931</v>
+        <v>0.4284736448183324</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3979793631619089</v>
+        <v>0.4110222594562742</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4277276149795028</v>
+        <v>0.4407938692799789</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6188155384647374</v>
+        <v>0.6319965477599752</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5291951600099765</v>
+        <v>0.5423938989647397</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5663052354285227</v>
+        <v>0.5797103630813538</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2184494497486114</v>
+        <v>0.2319067434588291</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3100735916389823</v>
+        <v>0.3235258803590924</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6053312875057486</v>
+        <v>0.6188873338573515</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6260886816022975</v>
+        <v>0.6156590459041453</v>
       </c>
     </row>
     <row r="15">
@@ -2685,514 +2685,514 @@
         <v>3313</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8117231648488854</v>
+        <v>0.8242454545245081</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.192301679865309</v>
+        <v>1.205211489441361</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7672488501174968</v>
+        <v>0.7802559815350989</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7465813669688899</v>
+        <v>0.7595605093673541</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4798172602577182</v>
+        <v>0.4929280646326575</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5056020896123812</v>
+        <v>0.5186449859067466</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.571788988096209</v>
+        <v>0.5848552423966851</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9497610375489387</v>
+        <v>0.9629420468441765</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7076564124593006</v>
+        <v>0.7208551514140638</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8234231682704873</v>
+        <v>0.8368282959233184</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4677492281967943</v>
+        <v>0.4812065219070121</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5021323855422253</v>
+        <v>0.5155846742623353</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8364808533778927</v>
+        <v>0.8500368997294956</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6938085846882842</v>
+        <v>0.6833789489901321</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03764</t>
+          <t>X &gt; -0.03765</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3079</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7056522936256897</v>
+        <v>0.7181745833013125</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.302587936913454</v>
+        <v>1.315497746489505</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5504603800407963</v>
+        <v>0.5634675114583985</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8431038991374322</v>
+        <v>0.8560830415358964</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3046826840652628</v>
+        <v>0.3177934884402021</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1799096169092067</v>
+        <v>0.1929525132035721</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5498689818064548</v>
+        <v>0.5629352361069309</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7972032835770904</v>
+        <v>0.8103842928723282</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8336376292882548</v>
+        <v>0.846836368243018</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8604205313015783</v>
+        <v>0.8738256589544093</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4283206658992285</v>
+        <v>0.4417779596094462</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4302257459468422</v>
+        <v>0.4436780346669522</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7569669128518868</v>
+        <v>0.7705229592034897</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5519951629586402</v>
+        <v>0.541565527260488</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02061</t>
+          <t>X &gt; -0.02062</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2759</v>
+        <v>2760</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.076695786350378</v>
+        <v>1.106040491204773</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.56733311938104</v>
+        <v>1.560071789445296</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9549943149229136</v>
+        <v>0.9479091003424358</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.230227512771442</v>
+        <v>1.223061780162681</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5105812161479761</v>
+        <v>0.5036128067771344</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6267980723123543</v>
+        <v>0.6198274161223623</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9407595344529085</v>
+        <v>0.9336677814938739</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.089741412945777</v>
+        <v>1.118773050750612</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.064986543073729</v>
+        <v>1.094022778285805</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.157231782112504</v>
+        <v>1.186132967463195</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6987633436231206</v>
+        <v>0.7278086207972052</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6606564683480372</v>
+        <v>0.6897230050365835</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.037792216228794</v>
+        <v>1.066673600998541</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8163283364717415</v>
+        <v>0.8213947584714489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003583</t>
+          <t>X &gt; -0.00359</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.362283072824852</v>
+        <v>1.352486373112562</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.243246773293421</v>
+        <v>1.274661241507495</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.097134285602309</v>
+        <v>1.128542985637665</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.393224897480124</v>
+        <v>1.424536881816167</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.062100531495844</v>
+        <v>1.093458269458139</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8620300314005647</v>
+        <v>0.8935260413228079</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.399186861391968</v>
+        <v>1.430448504269656</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.305137790968679</v>
+        <v>1.33635955381073</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.119759795333643</v>
+        <v>1.151050832845357</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.347578225562764</v>
+        <v>1.378628928351375</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7282312030693916</v>
+        <v>0.7595058886158483</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9284518396851382</v>
+        <v>0.959652793561304</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.005709666551176</v>
+        <v>1.036808198018299</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.757918561016524</v>
+        <v>0.7652375904744275</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01345</t>
+          <t>X &gt; 0.01344</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2109</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.987358265849771</v>
+        <v>1.999880555525394</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.845675596460673</v>
+        <v>1.858585406036724</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.640470237422157</v>
+        <v>1.653477368839759</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.960386717587745</v>
+        <v>1.97336585998621</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.327133828736535</v>
+        <v>1.340244633111475</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9133382131093697</v>
+        <v>0.9263811094037351</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.302762864732308</v>
+        <v>1.315829119032784</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.357153671735539</v>
+        <v>1.370334681030776</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.343569622442764</v>
+        <v>1.356768361397528</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.584008685873819</v>
+        <v>1.59741381352665</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.04734450332959</v>
+        <v>1.060801797039808</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.081727660675021</v>
+        <v>1.095179949395131</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.514958113741507</v>
+        <v>1.52851416009311</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.195689403343536</v>
+        <v>1.185259767645384</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.03047</t>
+          <t>X &gt; 0.03046</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.922359814732431</v>
+        <v>1.95987344314986</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.84671598783509</v>
+        <v>1.828950507980771</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.945538998188582</v>
+        <v>1.927600175857314</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.801518954712712</v>
+        <v>1.783702512428121</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9888245635571593</v>
+        <v>0.9712901523148858</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7377201491060603</v>
+        <v>0.7204185679148836</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.31124205443389</v>
+        <v>1.293602945490825</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.337750372602478</v>
+        <v>1.319955354335654</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.221895851203492</v>
+        <v>1.204148636409386</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.578572640942433</v>
+        <v>1.615194752360217</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8801275996747719</v>
+        <v>0.9170725414684497</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8048014865868538</v>
+        <v>0.8418015710167523</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.317075674325437</v>
+        <v>1.353668261563001</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7988321135682668</v>
+        <v>0.7570354907368966</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0475</t>
+          <t>X &gt; 0.04749</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.548308629051434</v>
+        <v>2.589687307077973</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.056195517050561</v>
+        <v>3.032416490009005</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.23936149253489</v>
+        <v>3.27949362900236</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.690745004076241</v>
+        <v>3.730643034464919</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.959645561643768</v>
+        <v>2.999798924244715</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.614826741491726</v>
+        <v>2.655324430131401</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.915449478940069</v>
+        <v>2.955723185114266</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.962074686452723</v>
+        <v>3.002133360326248</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.836848724483652</v>
+        <v>2.876966351428628</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.564758221536643</v>
+        <v>2.604711226472332</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.846196290924915</v>
+        <v>1.886531249213419</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.495222993549724</v>
+        <v>1.535800287319702</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.781455216259289</v>
+        <v>1.821682810129531</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9393332601605024</v>
+        <v>0.9562759699837997</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.06453</t>
+          <t>X &gt; 0.06452</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1306</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.56016045467517</v>
+        <v>2.572682744350793</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.709689445079974</v>
+        <v>2.722599254656025</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.00394784414955</v>
+        <v>3.016954975567153</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.206176474459951</v>
+        <v>4.219155616858416</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.055197832128975</v>
+        <v>3.068308636503914</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.35723395054908</v>
+        <v>2.370276846843446</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.502209268498859</v>
+        <v>2.515275522799335</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.030431689012914</v>
+        <v>3.043612698308152</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.58658341079385</v>
+        <v>2.599782149748613</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.349015653024736</v>
+        <v>2.362420780677567</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.531704901448343</v>
+        <v>1.545162195158561</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.10666998834968</v>
+        <v>1.12012227706979</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.452112161478283</v>
+        <v>1.465668207829886</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.242415423310469</v>
+        <v>1.231985787612317</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.08156</t>
+          <t>X &gt; 0.08155</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1075</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.948422144906303</v>
+        <v>2.960944434581926</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.918243880779258</v>
+        <v>2.931153690355309</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.174537964880344</v>
+        <v>3.187545096297946</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.886186446325048</v>
+        <v>4.899165588723513</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.603579184741257</v>
+        <v>3.616689989116196</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.342881587573189</v>
+        <v>3.355924483867554</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.188380428440446</v>
+        <v>4.201446682740922</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.372359820356621</v>
+        <v>4.385540829651859</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.218336678360366</v>
+        <v>4.231535417315129</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.205420795658021</v>
+        <v>4.218825923310852</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.349504680642767</v>
+        <v>3.362961974352984</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.639701791476568</v>
+        <v>2.653154080196678</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.521772761927018</v>
+        <v>3.535328808278621</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.12033130350563</v>
+        <v>3.109901667807478</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.09859</t>
+          <t>X &gt; 0.09857</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>937</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.002826354283094</v>
+        <v>3.015348643958717</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.312277287743591</v>
+        <v>3.325187097319642</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.810684995234517</v>
+        <v>2.823692126652119</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.648515502441796</v>
+        <v>4.661494644840261</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.363029185982228</v>
+        <v>3.376139990357167</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.23357678004794</v>
+        <v>3.246619676342306</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.682460992338086</v>
+        <v>3.695527246638562</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.38923703859394</v>
+        <v>4.402418047889178</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.687895636936723</v>
+        <v>3.701094375891486</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.118453482858634</v>
+        <v>4.131858610511465</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.59352940080359</v>
+        <v>3.606986694513807</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.774123870849131</v>
+        <v>2.787576159569241</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.847999462679049</v>
+        <v>3.861555509030651</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.35065569356793</v>
+        <v>3.340226057869778</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>777</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.491117664346007</v>
+        <v>3.503639954021629</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.453546625384327</v>
+        <v>4.466456434960378</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.672577532687356</v>
+        <v>3.685584664104958</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.218532080996262</v>
+        <v>5.231511223394726</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.393109578922804</v>
+        <v>3.406220383297743</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.19011638366478</v>
+        <v>2.203182637965256</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.881234143184429</v>
+        <v>2.894415152479667</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.691534128301996</v>
+        <v>2.704732867256759</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.38581048767562</v>
+        <v>3.399215615328451</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.052357034657909</v>
+        <v>3.065814328368127</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.443239548502703</v>
+        <v>2.456691837222813</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.824786739359595</v>
+        <v>3.838342785711198</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.173607170734982</v>
+        <v>3.16317753503683</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>629</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.514510805386216</v>
+        <v>2.527033095061839</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.446657383200964</v>
+        <v>3.459567192777016</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.574841140833307</v>
+        <v>2.587848272250909</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.294919392677699</v>
+        <v>4.307898535076163</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.120568129910772</v>
+        <v>3.133678934285712</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.623097508007987</v>
+        <v>2.636140404302353</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.061416254964648</v>
+        <v>2.074482509265124</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.866092951572654</v>
+        <v>2.879273960867891</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.805093065390352</v>
+        <v>2.818291804345115</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.180723047294066</v>
+        <v>4.194128174946897</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.929864794518608</v>
+        <v>4.943322088228825</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.169335392245607</v>
+        <v>4.182787680965717</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.292800972079711</v>
+        <v>6.306357018431314</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.952697185119113</v>
+        <v>4.942267549420961</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>529</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.894085309279625</v>
+        <v>2.906607598955247</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.265714823367176</v>
+        <v>1.278721954784778</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.853434874689228</v>
+        <v>3.866414017087692</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.991762241847681</v>
+        <v>2.00487304622262</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.154988678618167</v>
+        <v>1.168031574912533</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.204470462291063</v>
+        <v>2.217536716591539</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.438610314927338</v>
+        <v>3.451791324222576</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.810502678272442</v>
+        <v>2.823701417227205</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.228808495134871</v>
+        <v>4.242213622787702</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.347306588586669</v>
+        <v>5.360763882296887</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.247474244986925</v>
+        <v>4.260926533707035</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.040830220053358</v>
+        <v>7.054386266404961</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.967300134560269</v>
+        <v>5.956870498862116</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>435</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.449090415422205</v>
+        <v>2.461612705097828</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.906482319699329</v>
+        <v>2.91939212927538</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.821958440688945</v>
+        <v>1.834965572106547</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.791292033066561</v>
+        <v>3.804271175465026</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9540202432817466</v>
+        <v>0.9671310476566859</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1020368936410918</v>
+        <v>0.1150797899354572</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.166728463725129</v>
+        <v>1.179794718025605</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.30874046724248</v>
+        <v>2.321921476537717</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.707510696002714</v>
+        <v>2.720709434957477</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.466580913273631</v>
+        <v>3.479986040926462</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.641137933783639</v>
+        <v>4.654595227493857</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.066325688830219</v>
+        <v>3.079777977550329</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.094346939954285</v>
+        <v>6.107902986305888</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.884298157288036</v>
+        <v>5.873868521589884</v>
       </c>
     </row>
     <row r="29">
@@ -3413,98 +3413,98 @@
         <v>359</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.938316554441833</v>
+        <v>2.950838844117456</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.998052133678136</v>
+        <v>3.010961943254188</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.046080363014696</v>
+        <v>2.059087494432298</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.126194219856181</v>
+        <v>4.139173362254645</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.752118408683721</v>
+        <v>2.76522921305866</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.8211480901319774</v>
+        <v>0.8341909864263428</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.850620500993408</v>
+        <v>1.863686755293884</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.661988634245326</v>
+        <v>1.675169643540563</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.879540280096457</v>
+        <v>1.89273901905122</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.257827351335941</v>
+        <v>3.271232478988772</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.00293475125234</v>
+        <v>5.016392044962558</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.251802588263516</v>
+        <v>2.265254876983626</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.895614829686302</v>
+        <v>4.909170876037905</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.309681565862313</v>
+        <v>4.299251930164161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.2008</t>
+          <t>X &gt; 0.2007</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>282</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.761880828726191</v>
+        <v>1.774403118401814</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.568746932073992</v>
+        <v>1.581656741650043</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.173878225477402</v>
+        <v>1.186885356895004</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.431790932552993</v>
+        <v>3.444770074951457</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.7657101430127327</v>
+        <v>0.7788209473876719</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.064507493739683</v>
+        <v>-1.051464597445317</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.333028292534131</v>
+        <v>1.346094546834607</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.8658448937526302</v>
+        <v>0.879025903047868</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.159454936648338</v>
+        <v>1.172653675603101</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.082379397010484</v>
+        <v>2.095784524663316</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.296065789004963</v>
+        <v>3.309523082715181</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4935695137262854</v>
+        <v>0.5070218024463955</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.846364548171451</v>
+        <v>1.859920594523054</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.741475951369722</v>
+        <v>1.73104631567157</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>234</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.877894049731751</v>
+        <v>1.890803859307802</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2009740610838833</v>
+        <v>0.2139811925014854</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3312271936913831</v>
+        <v>0.3442063360898473</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.061894876081645</v>
+        <v>-1.048784071706706</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.619153793066836</v>
+        <v>-1.606110896772471</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.03431877236847924</v>
+        <v>-0.02113776307324144</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.7593821961500709</v>
+        <v>0.7725809351048341</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.191308293173421</v>
+        <v>1.204713420826252</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.9865549688558417</v>
+        <v>1.000012262566059</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.543164437901282</v>
+        <v>-1.529712149181172</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6813677667949065</v>
+        <v>-0.6678117204433036</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.004296007168193228</v>
+        <v>-0.01472564286634537</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>189</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.474815648043993</v>
+        <v>1.487337937719616</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1367579649202639</v>
+        <v>-0.1238481553442128</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.002526142416321875</v>
+        <v>0.01048098900128025</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.244129106593292</v>
+        <v>2.257108248991756</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4106942248809915</v>
+        <v>-0.3975834205060522</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.216611507273079</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.256187062638666</v>
+        <v>-1.24312080833819</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.723370461420167</v>
+        <v>-1.710189452124929</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.255269818501944</v>
+        <v>-1.242071079547181</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.047193945328814</v>
+        <v>-1.033788817675983</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.781047798746918</v>
+        <v>-1.767590505036701</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.863066757803601</v>
+        <v>-3.849614469083491</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.225120310547446</v>
+        <v>-3.211564264195843</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.446298449170634</v>
+        <v>-2.456728084868786</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.798993875765532</v>
+        <v>-1.78647158608991</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.716123044285347</v>
+        <v>-2.703213234709295</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.722102861993044</v>
+        <v>-1.709095730575442</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2029608404966581</v>
+        <v>-0.1899816980981939</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.519159833346606</v>
+        <v>-3.506049028971667</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.916162340075388</v>
+        <v>-3.903119443781023</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.917562724014331</v>
+        <v>-1.904496469713855</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.773635011684725</v>
+        <v>-3.760454002389487</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.445746008978134</v>
+        <v>-2.43254727002337</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.601426749561618</v>
+        <v>-2.588021621908787</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.195068962768083</v>
+        <v>-4.181611669057865</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.021796916533766</v>
+        <v>-9.008344627813656</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.442051527478668</v>
+        <v>-9.428495481127065</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-8.497885750757931</v>
+        <v>-8.508315386456083</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2689</t>
+          <t>X &gt; 0.2688</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.952106234245477</v>
+        <v>2.9646285239211</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.310829650984182</v>
+        <v>4.323739460560233</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.93576292458561</v>
+        <v>1.948770056003212</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.056115067094098</v>
+        <v>3.069094209492562</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4526031776810342</v>
+        <v>-0.4394923733060949</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.125458269668343</v>
+        <v>-3.112415373373977</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7502040526633422</v>
+        <v>0.7632703069638183</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7070783560191529</v>
+        <v>-0.6938973467239151</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.22202076769954</v>
+        <v>0.2352195066543032</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.608302437130369</v>
+        <v>-2.594897309477538</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-5.783352791150925</v>
+        <v>-5.769895497440707</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.69946468331044</v>
+        <v>-10.68601239459033</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-14.09001632395832</v>
+        <v>-14.07646027760671</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-13.84029499168203</v>
+        <v>-13.85072462738018</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.521494090922161</v>
+        <v>2.534403900498212</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.126625384325571</v>
+        <v>2.139632515743173</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.461697794041491</v>
+        <v>3.474676936439955</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.896000529464402</v>
+        <v>-1.882889725089463</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.213016423074052</v>
+        <v>-5.199973526779686</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4784730319125927</v>
+        <v>-0.4654067776121167</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-2.150475707802521</v>
+        <v>-2.137294698507283</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.006656316876395</v>
+        <v>-0.9934575779216317</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.856781501904322</v>
+        <v>-1.843376374251491</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.675992657547205</v>
+        <v>-5.662535363836987</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-10.46088660863551</v>
+        <v>-10.44743431991539</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-14.4955990509057</v>
+        <v>-14.4820430045541</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-14.24587771862942</v>
+        <v>-14.25630735432757</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-14-50 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-14-50 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.095847958764196</v>
+        <v>-3.083325669088573</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.092963740403142</v>
+        <v>-1.080053930827091</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.487832446999732</v>
+        <v>-1.47482531558213</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1527600372838052</v>
+        <v>-0.139780894885341</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.128095856077763</v>
+        <v>4.141206660452703</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3937393146403139</v>
+        <v>-0.3806964183459485</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.750442630738007</v>
+        <v>6.763508885038483</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.668801400631203</v>
+        <v>2.681982409926441</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.427078622882647</v>
+        <v>7.44027736183741</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.19141126918002</v>
+        <v>10.20481639683285</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>20.83003143883835</v>
+        <v>20.84348873254856</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>20.86441459618378</v>
+        <v>20.87786688490389</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.23934070813043</v>
+        <v>19.25289675448204</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>18.28424276329828</v>
+        <v>18.27381312760013</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.461516634744982</v>
+        <v>2.474038924420604</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.852759680921984</v>
+        <v>-1.839849871345933</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.049430189320375</v>
+        <v>-4.036423057902773</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.216474354010167</v>
+        <v>-1.203495211611703</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04690623271946492</v>
+        <v>0.0600170370944042</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.259255433168484</v>
+        <v>-3.246212536874118</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2596144531628468</v>
+        <v>0.2726807074633228</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.009370747420455</v>
+        <v>-1.996189738125217</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.434133870901746</v>
+        <v>2.44733260985651</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.48490958677472</v>
+        <v>2.498314714427551</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.19006617236705</v>
+        <v>12.20352346607727</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.12535023061338</v>
+        <v>13.13880251933349</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.70509561966848</v>
+        <v>12.71865166602008</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.85571785284567</v>
+        <v>13.84528821714752</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06130620533747333</v>
+        <v>0.07382849501309607</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.550267407626784</v>
+        <v>-1.537357598050733</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.675063121522641</v>
+        <v>-2.662055990105038</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.814882981615874</v>
+        <v>-1.80190383921741</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.8934501820895093</v>
+        <v>-0.88033937771457</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.515716273570924</v>
+        <v>-3.502673377276558</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6807419616461274</v>
+        <v>-0.6676757073456514</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.147925360427628</v>
+        <v>-1.13474435113239</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2509287679886114</v>
+        <v>0.2641275069433746</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.05043861945704</v>
+        <v>3.063843747109871</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.14495536813216</v>
+        <v>10.15841266184238</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.63919254007612</v>
+        <v>11.65264482879623</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.48901092183196</v>
+        <v>10.50256696818356</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>12.92851327600606</v>
+        <v>12.91808364030791</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3722261989978506</v>
+        <v>-0.3597039093222278</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.589860418022717</v>
+        <v>-2.576950608446666</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.180775994962772</v>
+        <v>-2.167665190587833</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.701515875428925</v>
+        <v>-3.688472979134559</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.435251173300891</v>
+        <v>-2.422070164005653</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.5340519708198528</v>
+        <v>0.547250709774616</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.10816921003434</v>
+        <v>2.121574337687171</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>9.782203764504644</v>
+        <v>9.795661058214861</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.816586921850075</v>
+        <v>9.830039210570185</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.396332310905173</v>
+        <v>9.409888357256776</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>203</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.261911226613911</v>
+        <v>-1.249388936938288</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.380874002139748</v>
+        <v>-2.367964192563697</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.297910196421064</v>
+        <v>-1.284903065003462</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3101754485017025</v>
+        <v>0.3231545909001667</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.742197583183227</v>
+        <v>1.755308387558166</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.06919617114519383</v>
+        <v>0.08223906743955922</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4770732913113349</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.4827209449085856</v>
+        <v>-0.4695399356133478</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.9341116812243797</v>
+        <v>0.9473104201791429</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.561819008511726</v>
+        <v>1.575224136164557</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.253617408332076</v>
+        <v>8.267074702042294</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>8.288000565677507</v>
+        <v>8.301452854397617</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.360356792171025</v>
+        <v>8.373912838522628</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.610078124447313</v>
+        <v>8.59964848874916</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>269</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.5751537375517586</v>
+        <v>0.5876760272273813</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.397430705737406</v>
+        <v>-1.384520896161355</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.817808890915103</v>
+        <v>1.830816022332705</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.587051193197688</v>
+        <v>1.600030335596152</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.976009248779</v>
+        <v>1.783762443150273</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.199537561049901</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.509039060251681</v>
+        <v>1.317725752508373</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.784963678064692</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.129417389714675</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.597937744083325</v>
+        <v>2.395638508810173</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.425301407602291</v>
+        <v>7.203689683955659</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>8.068248519236576</v>
+        <v>7.843507224038198</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.904499484499858</v>
+        <v>6.918055530851461</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.154220816776146</v>
+        <v>7.143791181077994</v>
       </c>
     </row>
     <row r="12">
@@ -4220,101 +4220,101 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3312761580478139</v>
+        <v>-0.3187538683721911</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.801488897943884</v>
+        <v>-1.92993996143602</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1196845776204896</v>
+        <v>-0.01532879290606814</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1461942646565078</v>
+        <v>-0.2805614082431163</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.102880239513141</v>
+        <v>0.9633727088424493</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.9119766475335283</v>
+        <v>-1.04565131991945</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.257616713245056</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.718997729774713</v>
+        <v>-1.852639594575074</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5273911900708228</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6719869219223398</v>
+        <v>-0.8116250596006154</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.443819926120803</v>
+        <v>3.291841701209904</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.644560248430636</v>
+        <v>3.491655372186344</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.553603345271185</v>
+        <v>2.402207087737061</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.689089039158034</v>
+        <v>2.79289504184932</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.08872</t>
+          <t>X &lt; -0.08873</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.576941375199794</v>
+        <v>-1.667907900453045</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.084603769908924</v>
+        <v>-3.175605178588</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.9211485334313565</v>
+        <v>-1.017485753251179</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4761848842125076</v>
+        <v>-0.5734172809202747</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3280909081546568</v>
+        <v>0.2280129018115815</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.112664397688555</v>
+        <v>-1.209473539149485</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.324206481173547</v>
+        <v>-2.418899761894934</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.889796627846337</v>
+        <v>-2.984394437670119</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.600335380958803</v>
+        <v>-1.697928353586271</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.716802498754795</v>
+        <v>-1.815937425911549</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.894154876455751</v>
+        <v>0.7889969063224882</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4226475279106765</v>
+        <v>0.3182896988206707</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7143781338345079</v>
+        <v>-0.8173843700159509</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.7660168525710489</v>
+        <v>-0.6838547044797494</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.802080295518621</v>
+        <v>-2.86612404286101</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.645970202107769</v>
+        <v>-4.709386074215466</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.332697977232122</v>
+        <v>-2.400320185323856</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.586681770729214</v>
+        <v>-2.653861987055883</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.95773816322928</v>
+        <v>-2.026720863596985</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.88898936616836</v>
+        <v>-1.957812335430432</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.735838944159717</v>
+        <v>-1.805135833805792</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.900433416954257</v>
+        <v>-2.96865753302292</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.098523786755912</v>
+        <v>-2.168203362933752</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.709016733912158</v>
+        <v>-2.778993844131008</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9492486910857494</v>
+        <v>-1.022378492219062</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.612935936244213</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.047921548443021</v>
+        <v>-3.118535599738614</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.343686275692313</v>
+        <v>-3.280327965072438</v>
       </c>
     </row>
     <row r="15">
@@ -4376,517 +4376,517 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.915633736374026</v>
+        <v>-2.962843741377725</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.467330773753943</v>
+        <v>-4.514297539762232</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.10931232054471</v>
+        <v>-3.158371092894285</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.916843003531355</v>
+        <v>-2.966080045538746</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.695927510114281</v>
+        <v>-1.747238159991305</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.819344648597493</v>
+        <v>-1.870291160952746</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.839933454404509</v>
+        <v>-1.891012111569296</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.459360883541983</v>
+        <v>-3.509002672566339</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.23935813511158</v>
+        <v>-2.290617018604074</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.024868483978956</v>
+        <v>-3.076078192486676</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.699647717346842</v>
+        <v>-1.752749880439978</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.965290532399024</v>
+        <v>-2.018112637581666</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.175901656677638</v>
+        <v>-3.227734818263706</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.738081829189312</v>
+        <v>-2.691811918483836</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03764</t>
+          <t>X &lt; -0.03765</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.787887990953152</v>
+        <v>-1.82302129369225</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.54004018176181</v>
+        <v>-3.574698548809849</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.625234079921619</v>
+        <v>-1.662014751291075</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.388495431691616</v>
+        <v>-2.424508873718679</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7059712906963043</v>
+        <v>-0.7439945216341357</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3572986559754128</v>
+        <v>-0.3954864566862781</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.242171154583026</v>
+        <v>-1.279627744656096</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.037523900573611</v>
+        <v>-2.074603061571658</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.953381606661132</v>
+        <v>-1.99062807810418</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.278582558121599</v>
+        <v>-2.31616801474712</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.102713787079573</v>
+        <v>-1.141605343947177</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.205996325067773</v>
+        <v>-1.244811864280891</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.049621037997753</v>
+        <v>-2.087980060763741</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.557409560281741</v>
+        <v>-1.524886905644166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02061</t>
+          <t>X &lt; -0.02062</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1370</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.95113897096919</v>
+        <v>-2.010923261192346</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.947269530858748</v>
+        <v>-2.934359721282696</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.929279626012679</v>
+        <v>-1.916272494595077</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.413105768032885</v>
+        <v>-2.400126625634421</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.8833931747373001</v>
+        <v>-0.8702823703623608</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.127297640833334</v>
+        <v>-1.114254744538968</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.608920748705685</v>
+        <v>-1.595854494405209</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.964849481968962</v>
+        <v>-2.024342891278373</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.768978332210459</v>
+        <v>-1.828506865982966</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.143517967417026</v>
+        <v>-2.202893043548769</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.289327277893122</v>
+        <v>-1.348703196127545</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.28775091718164</v>
+        <v>-1.347184925837631</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.959678563705268</v>
+        <v>-2.019061977601659</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.597034169249426</v>
+        <v>-1.607463804947578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003583</t>
+          <t>X &lt; -0.00359</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1717</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.741993233504772</v>
+        <v>-1.729470943829149</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.589106785690134</v>
+        <v>-1.63403387605625</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.548491750881936</v>
+        <v>-1.593354989834694</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.908712625866272</v>
+        <v>-1.953637363027738</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.373865639964343</v>
+        <v>-1.418692263167621</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.103360407708237</v>
+        <v>-1.148288525906629</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.737103842859398</v>
+        <v>-1.782042228930145</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.651206431043725</v>
+        <v>-1.696063727029973</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.274627154932453</v>
+        <v>-1.319500425269212</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.744770412806503</v>
+        <v>-1.789471037623173</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9295650867990943</v>
+        <v>-0.9742473279725914</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.270197149227194</v>
+        <v>-1.314918217109764</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.309209721761427</v>
+        <v>-1.353860893104823</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.027248981198625</v>
+        <v>-1.037678616896777</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01345</t>
+          <t>X &lt; 0.01344</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.927771817504613</v>
+        <v>-1.94010973751567</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.792019807189988</v>
+        <v>-1.804841917006932</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.717999792897359</v>
+        <v>-1.730967996542198</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.005095487458888</v>
+        <v>-2.017898980225219</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.285574597050676</v>
+        <v>-1.298878804560069</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8630722677545464</v>
+        <v>-0.8765190385458226</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.167960136720581</v>
+        <v>-1.181288054197751</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.263214917355448</v>
+        <v>-1.276624588367667</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.149449712681836</v>
+        <v>-1.162941039903814</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.541725325612489</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.013943571435085</v>
+        <v>-1.027790852193569</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.100596784651145</v>
+        <v>-1.114402737331979</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.493566179191241</v>
+        <v>-1.507295349244444</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.2165326154444</v>
+        <v>-1.204794027392921</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.03047</t>
+          <t>X &lt; 0.03046</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2306</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.393826418528214</v>
+        <v>-1.424426164212669</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.344011070361468</v>
+        <v>-1.331101260785417</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.543471490008194</v>
+        <v>-1.530464358590592</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.390352895764359</v>
+        <v>-1.377373753365895</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6963856552808494</v>
+        <v>-0.6832748509059101</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.505161667838756</v>
+        <v>-0.4921187715443907</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8691407611954816</v>
+        <v>-0.8560745068950055</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9237695753140898</v>
+        <v>-0.910588566018852</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7449430857606743</v>
+        <v>-0.7317443468059111</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.138584036718903</v>
+        <v>-1.168468952356115</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6266049812465084</v>
+        <v>-0.6564564792209922</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.611436816398971</v>
+        <v>-0.6413120840046815</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9642304033636506</v>
+        <v>-0.9940206942465579</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6036244035477552</v>
+        <v>-0.5706889048139914</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0475</t>
+          <t>X &lt; 0.04749</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2572</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.455770962836091</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.744330818623141</v>
+        <v>-1.731421009047089</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.964069567374381</v>
+        <v>-1.989777108817798</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.200766159370914</v>
+        <v>-2.226516683897316</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.711613232115383</v>
+        <v>-1.737247100347957</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.509831590721376</v>
+        <v>-1.535548384349497</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.612750350570714</v>
+        <v>-1.63845881515352</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.671445545259417</v>
+        <v>-1.697054295467666</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.517664260174612</v>
+        <v>-1.543270333016515</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.454083754392528</v>
+        <v>-1.479498502516094</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.055101325227632</v>
+        <v>-1.080478982973723</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8827137774506326</v>
+        <v>-0.9081115275805587</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.009396174885502</v>
+        <v>-1.034705266505135</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5436348435521339</v>
+        <v>-0.554064479250286</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.06453</t>
+          <t>X &lt; 0.06452</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.083001084666961</v>
+        <v>-1.088600203956979</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.159685654514625</v>
+        <v>-1.165444859846417</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.394728910765885</v>
+        <v>-1.400453755266795</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.916397715423116</v>
+        <v>-1.921927122704169</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.34166454144453</v>
+        <v>-1.347461744193069</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.025301238776272</v>
+        <v>-1.031179707434504</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.020428841014727</v>
+        <v>-1.026322287053624</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.291898237795237</v>
+        <v>-1.297752785271307</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.015602994676698</v>
+        <v>-1.021565768904011</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.997596619466897</v>
+        <v>-1.003666757850951</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6520753321948405</v>
+        <v>-0.6582948432118627</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4918067493754563</v>
+        <v>-0.4980827736027607</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6090329564997532</v>
+        <v>-0.6153194732607901</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5519948545482336</v>
+        <v>-0.5467950842842271</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.08156</t>
+          <t>X &lt; 0.08155</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9446936185471131</v>
+        <v>-0.9489733968968039</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9412806872512007</v>
+        <v>-0.9457049928515247</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.123045403229227</v>
+        <v>-1.127447546187533</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.693387298286034</v>
+        <v>-1.697594531159638</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.202531255699412</v>
+        <v>-1.206948361724777</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.116158711365031</v>
+        <v>-1.120580538568262</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.346761606006417</v>
+        <v>-1.351118140372108</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.437033704495178</v>
+        <v>-1.441404309115676</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.317018392836331</v>
+        <v>-1.321436158912263</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.397389978978083</v>
+        <v>-1.401858750963306</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.126292384423301</v>
+        <v>-1.130870443856203</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9102495052481316</v>
+        <v>-0.9148978935425873</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.181458692417749</v>
+        <v>-1.186058017485415</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.077289811006786</v>
+        <v>-1.073099892729957</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.09859</t>
+          <t>X &lt; 0.09857</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7929703014892269</v>
+        <v>-0.7965741715200068</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8902803476561303</v>
+        <v>-0.8939741984811818</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.8314447983721323</v>
+        <v>-0.8351881150947875</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.340270855070884</v>
+        <v>-1.343847865233172</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.9249184504454249</v>
+        <v>-0.9286668372859097</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.891856784519824</v>
+        <v>-0.8955957532676422</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9597981448055535</v>
+        <v>-0.9635242474916268</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.191291880561103</v>
+        <v>-1.194982153547826</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.9226166863492864</v>
+        <v>-0.926397593141985</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.129969372284464</v>
+        <v>-1.13375025639251</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.004536881390933</v>
+        <v>-1.008374288999462</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7963046741348236</v>
+        <v>-0.8002069126336835</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.073919850546488</v>
+        <v>-1.077768423449477</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9634245978757292</v>
+        <v>-0.9599021909241898</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.7252362399722259</v>
+        <v>-0.7280936894767152</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9540012316284603</v>
+        <v>-0.9568866704035273</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8572996109275266</v>
+        <v>-0.8602385499703402</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.186998119893836</v>
+        <v>-1.189833021321505</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7277452411286731</v>
+        <v>-0.7307499345173056</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5332258321388821</v>
+        <v>-0.5362726058690299</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.39346494359026</v>
+        <v>-0.3965599617773492</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5764607677564584</v>
+        <v>-0.5795304470985627</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4722577754362831</v>
+        <v>-0.4753637613211055</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7101209622486806</v>
+        <v>-0.7132078000440245</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6599224153264558</v>
+        <v>-0.6630379702100342</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5493262347607626</v>
+        <v>-0.5524744506319976</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.8336742865335793</v>
+        <v>-0.8367642149771939</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.7164617253004977</v>
+        <v>-0.7136787426545155</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.372743757158446</v>
+        <v>-0.3750537653095378</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5457864206457614</v>
+        <v>-0.5481226189013455</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4696898109471235</v>
+        <v>-0.4720671302210988</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7513938889297123</v>
+        <v>-0.7536862457104618</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5050849148829712</v>
+        <v>-0.5074735303961617</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4201848917034141</v>
+        <v>-0.4225852618361827</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2613513372640242</v>
+        <v>-0.2638021836375799</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4277834556220981</v>
+        <v>-0.4302097290314393</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3590444714920054</v>
+        <v>-0.3614944716459902</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6798133553454804</v>
+        <v>-0.6822124603934938</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8402064639575428</v>
+        <v>-0.8425705731674569</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.732882645323663</v>
+        <v>-0.7352770983944268</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.080154926507518</v>
+        <v>-1.082470987187094</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8716952745674647</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3600</v>
+        <v>3601</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3484064907054147</v>
+        <v>-0.3503128207944499</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2844139265297159</v>
+        <v>-0.286400490606205</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1935942924985952</v>
+        <v>-0.1956221240785752</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5469128257228775</v>
+        <v>-0.5488388937042075</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2391653750479037</v>
+        <v>-0.2411983056721851</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1205846115708269</v>
+        <v>-0.1226400866183752</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2179354560477194</v>
+        <v>-0.2199682607953974</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4204273947499857</v>
+        <v>-0.4224230132634048</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2720674760762947</v>
+        <v>-0.2741076323824103</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5520063524719632</v>
+        <v>-0.5540025126469601</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7413498398149869</v>
+        <v>-0.7433023830793246</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.608261226485034</v>
+        <v>-0.6102504470383749</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9852956880513446</v>
+        <v>-0.9871974368306908</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.8570842469577968</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2139670496407859</v>
+        <v>-0.215543862249568</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2733875402978114</v>
+        <v>-0.2749993450710662</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.221877940715494</v>
+        <v>-0.2235167895188965</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4279428419365345</v>
+        <v>-0.429522858691989</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06062771224358698</v>
+        <v>-0.06232452693182466</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.03553043860280525</v>
+        <v>0.0338160739673512</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.03443804299718778</v>
+        <v>-0.03613702436899757</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1895509276006351</v>
+        <v>-0.1912234640965309</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1816205696702156</v>
+        <v>-0.1832980207741173</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3408204158076416</v>
+        <v>-0.3424822869533912</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5034496317789987</v>
+        <v>-0.5050748022830405</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3457507404875884</v>
+        <v>-0.3474183512530828</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6696864695926337</v>
+        <v>-0.6712804739120486</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.6755161423839908</v>
+        <v>-0.6739671681430579</v>
       </c>
     </row>
     <row r="29">
@@ -5104,101 +5104,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2068932501597445</v>
+        <v>-0.2081887578070791</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2181795693455726</v>
+        <v>-0.2195142303917308</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2020758262294251</v>
+        <v>-0.2034255971950998</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3749185124543288</v>
+        <v>-0.3762199066849803</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2110389312855006</v>
+        <v>-0.212398235320876</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.03146438113179784</v>
+        <v>-0.0328642322318089</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07527166409022357</v>
+        <v>-0.07666281287013987</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.07777813786174903</v>
+        <v>-0.07918138743934833</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.04471583973604254</v>
+        <v>-0.04613013254690657</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2442902012485959</v>
+        <v>-0.2456743077071692</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.434246451945576</v>
+        <v>-0.4355862318559574</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1994804324993567</v>
+        <v>-0.2008822489227029</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4192459056276974</v>
+        <v>-0.4206010543567089</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3933322582734036</v>
+        <v>-0.3920995285934481</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.2008</t>
+          <t>X &lt; 0.2007</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.05820515958821204</v>
+        <v>-0.05926360888193472</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.04955715214288148</v>
+        <v>-0.05065134639610847</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.09345243863033659</v>
+        <v>-0.09454388928092072</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.234289161298662</v>
+        <v>-0.2353419884040449</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.006596440077814236</v>
+        <v>-0.007719872747770751</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1235047589302383</v>
+        <v>0.1223531242226699</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.001078802826469882</v>
+        <v>-4.337849033930752e-05</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.01525964471576913</v>
+        <v>0.0141236370039266</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.04646582902810081</v>
+        <v>0.04531990418431064</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.08819064927020293</v>
+        <v>-0.0893196489077468</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2004802181793366</v>
+        <v>-0.2015848362006025</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.02162371137225705</v>
+        <v>-0.0227746422436681</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.08942967485680953</v>
+        <v>-0.09057221101362245</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1109392123297184</v>
+        <v>-0.1100132381539396</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.01135029564497358</v>
+        <v>-0.01225396862594152</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.04819084282358688</v>
+        <v>-0.04911338255417519</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01959390141956163</v>
+        <v>-0.02053104610596534</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.003430324064723322</v>
+        <v>-0.004369818937924208</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1124430810432031</v>
+        <v>0.1114641307950137</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1421475070507512</v>
+        <v>0.141165619971261</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.04581787852568198</v>
+        <v>0.04485872714326433</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.07972167748329184</v>
+        <v>0.07874526863961506</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.08416852093638738</v>
+        <v>0.08318943566462877</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.007991110793845735</v>
+        <v>-0.008961792848964478</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.01878197798956904</v>
+        <v>-0.01975392775667473</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1070201222139957</v>
+        <v>0.106016012970791</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.0862395973217005</v>
+        <v>0.08523302798251109</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.01676979053431893</v>
+        <v>0.01752308034746619</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.001659924055154249</v>
+        <v>-0.00241324854142988</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.07008928140066217</v>
+        <v>0.06929428419336858</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.007347103957108914</v>
+        <v>-0.008128569081968351</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.09114649450508949</v>
+        <v>-0.09190526175296299</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.06789455454343596</v>
+        <v>0.06708739859514878</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1504735896170288</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1564456649167809</v>
+        <v>0.1556183563584099</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1593210056605514</v>
+        <v>0.1584858394031556</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1883900281997271</v>
+        <v>0.1875462142363489</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1129636042810702</v>
+        <v>0.1121262445888931</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1253511910910774</v>
+        <v>0.1245073302659989</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1994105923449823</v>
+        <v>0.1985480371058941</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1994664177693011</v>
+        <v>0.1985973651438684</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1336709328292116</v>
+        <v>0.1342668684707533</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.132874836368309</v>
+        <v>0.1322372577877289</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1606873412816014</v>
+        <v>0.16002393943333</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.05467391478373429</v>
+        <v>0.05403217090622547</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.02336373188549601</v>
+        <v>0.02273101461452143</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.174575213668362</v>
+        <v>0.1738981271957698</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1852860279019097</v>
+        <v>0.1846093716643651</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1643789370856439</v>
+        <v>0.1637062183235471</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2120689333026107</v>
+        <v>0.2113785516074032</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2150727044721563</v>
+        <v>0.214380539770886</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.155982514804279</v>
+        <v>0.1552950029867901</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1910059285726007</v>
+        <v>0.1903069404516202</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.3398785286631281</v>
+        <v>0.3391422773462764</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3854001088038785</v>
+        <v>0.3846472326928421</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.323214207418566</v>
+        <v>0.3236381174743315</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2689</t>
+          <t>X &lt; 0.2688</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.006430153914507741</v>
+        <v>-0.006893269524951506</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04560599258017106</v>
+        <v>-0.04607391275927597</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.05571129092209759</v>
+        <v>-0.05618043904628678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06056361414697875</v>
+        <v>-0.06103063760467364</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05851060399686503</v>
+        <v>0.05800908560651408</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1218015405545003</v>
+        <v>0.1212867434317033</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07541538420541372</v>
+        <v>0.07491108452025941</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09280579699704106</v>
+        <v>0.09229279645396815</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1198930245508123</v>
+        <v>0.1193725228483373</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1267478536129829</v>
+        <v>0.1262178469178394</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1840139777760257</v>
+        <v>0.1834676960214949</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2820354518147283</v>
+        <v>0.2814649038713455</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3970317851712863</v>
+        <v>0.3964286986358303</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.36300468287331</v>
+        <v>0.3633028811040973</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.03181420504255783</v>
+        <v>0.0313992404016048</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.01031581448471286</v>
+        <v>0.009893441812018011</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05078031933700089</v>
+        <v>-0.05119090608609866</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.05503184641381154</v>
+        <v>-0.0554405757582046</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.08578604965106962</v>
+        <v>0.08533821626173221</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1501233585487398</v>
+        <v>0.1496617591234894</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.103573882614505</v>
+        <v>0.1031228911368771</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1188186463168108</v>
+        <v>0.1183600448183455</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1455208935699304</v>
+        <v>0.1450550114288589</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09919053438900249</v>
+        <v>0.09872924893242896</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1552850341035636</v>
+        <v>0.1548080840285522</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.228312877054293</v>
+        <v>0.227817936331121</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.340915279209419</v>
+        <v>0.3403890160183067</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3081366582056475</v>
+        <v>0.3084006995335358</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_14_50.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18.8869831406274</v>
+        <v>21.49508600667763</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.079670750552907</v>
+        <v>-2.234494850743353</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.59792490786734</v>
+        <v>-10.01514734130138</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.345789208510375</v>
+        <v>-2.499010973959102</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.0109830617032</v>
+        <v>-10.37882693930428</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.71699626994054</v>
+        <v>-10.10896846984459</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-18.93508695194567</v>
+        <v>-17.56676965175033</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-15.83995164210154</v>
+        <v>-14.33796072982788</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-12.33786722668477</v>
+        <v>-10.679394019245</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-20.32587576867202</v>
+        <v>-18.90523117073401</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-13.39809100624947</v>
+        <v>-11.71215433727909</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.797326095676056</v>
+        <v>-7.954974448385769</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.649150686654551</v>
+        <v>-4.649107383246921</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897327646</v>
+        <v>3.006275965706543</v>
       </c>
     </row>
     <row r="7">
@@ -627,150 +627,150 @@
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-10.14021272346846</v>
+        <v>-10.16940068325183</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2448733468473918</v>
+        <v>-0.2460603083680368</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.196912928534687</v>
+        <v>3.196782547969754</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.345642719768904</v>
+        <v>-4.346166423177046</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.883827534620451</v>
+        <v>-4.835425534618558</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.588105115596186</v>
+        <v>-4.564224027322986</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.673928494885772</v>
+        <v>-4.626027227084805</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.539344689123212</v>
+        <v>2.588525042882537</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-9.045080015131887</v>
+        <v>-8.971949368061381</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.472727812372405</v>
+        <v>5.571987143683785</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.426067549387575</v>
+        <v>1.525901981219107</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.305062728451347</v>
+        <v>5.428703394682529</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.041252226288769</v>
+        <v>1.189904311626535</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.959633331494381</v>
+        <v>9.131632091059295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1653</t>
+          <t>X ≈ -0.1654</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.472595178479331</v>
+        <v>-2.501714947065459</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.640059728409589</v>
+        <v>-7.64130846672132</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.210414615996704</v>
+        <v>6.210307932993715</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.779394481807707</v>
+        <v>2.778919559621627</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.447016846403159</v>
+        <v>-8.398639539883774</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.587976554376397</v>
+        <v>-4.564096855538494</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.456453993048825</v>
+        <v>2.504388215656959</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-8.707421810944759</v>
+        <v>-8.658289246402639</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.930245957386774</v>
+        <v>2.00341270246566</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.486350587200803</v>
+        <v>-2.387114434762552</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.014471582971979</v>
+        <v>8.114318845550997</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.9116358682505492</v>
+        <v>1.035269753578326</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.062463678117808</v>
+        <v>4.2111173750502</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.853553481692565</v>
+        <v>-2.681554722130763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1483</t>
+          <t>X ≈ -0.1484</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.095351866315639</v>
+        <v>-5.124494927019015</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.455556146252242</v>
+        <v>-1.456754389760818</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.849999633523581</v>
+        <v>-1.85016763205558</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.154144891180827</v>
+        <v>6.153694559229514</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18.7466243663191</v>
+        <v>18.79517163692982</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>16.42201505288149</v>
+        <v>16.4460123165519</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.206926558224559</v>
+        <v>3.254863408549056</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.996604049364485</v>
+        <v>8.045805245264759</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.681131179627769</v>
+        <v>2.754299186485582</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7963013066438407</v>
+        <v>-0.6970623274522012</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.628266985193235</v>
+        <v>1.72809990817462</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.663121840999075</v>
+        <v>1.78675577465863</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.874523051665186</v>
+        <v>4.023176066080779</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.469754788980111</v>
+        <v>1.641753548550376</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.285152073278169</v>
+        <v>5.579677556092371</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.44868202746153</v>
+        <v>1.308627565354691</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.61984585923545</v>
+        <v>10.34854415656751</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.718436631379667</v>
+        <v>5.089144627128825</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.092067793406095</v>
+        <v>1.905820276897217</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.757804320042602</v>
+        <v>3.527278813703269</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.975493471923876</v>
+        <v>2.118778813697155</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.844570960667255</v>
+        <v>5.70201309115356</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.073840304882026</v>
+        <v>1.617692192904855</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.027461986680606</v>
+        <v>0.7950115474376744</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.161820388320876</v>
+        <v>-0.7593466570642065</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.558297875855565</v>
+        <v>0.6493322196435614</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.439459077883896</v>
+        <v>-3.798445010990768</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.665927037787029</v>
+        <v>-3.550280590854008</v>
       </c>
     </row>
     <row r="11">
@@ -832,1245 +832,1245 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.154636433702038</v>
+        <v>-3.071337538847047</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.721591781577054</v>
+        <v>-3.58514959688636</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.757024949487409</v>
+        <v>-6.148793159594682</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.137734846424621</v>
+        <v>-7.104112769061565</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.578265529449077</v>
+        <v>-3.260996156308998</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.019555171777924</v>
+        <v>-9.49674631906035</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.229315717533261</v>
+        <v>-10.64622676207633</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-13.07182585696555</v>
+        <v>-14.37551386580616</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.639589735713677</v>
+        <v>-10.07396996456007</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.62154118671987</v>
+        <v>-11.99400225310112</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.577305716696934</v>
+        <v>-10.02709507248664</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.66535932526233</v>
+        <v>-11.05693404865183</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-11.2149244076831</v>
+        <v>-12.54736253883309</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-10.35756632278567</v>
+        <v>-12.77472242399038</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09727</t>
+          <t>X ≈ -0.09729</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.80805777056176</v>
+        <v>-4.831918580298613</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.984664107069626</v>
+        <v>-6.575225644556802</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.073650367856978</v>
+        <v>-3.194941581946381</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.464086381293974</v>
+        <v>-0.1060628959333343</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.002375934389477</v>
+        <v>-1.835809987512619</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.70500190475439</v>
+        <v>-0.2688962384712852</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.921943668979608</v>
+        <v>-4.880424558972713</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.38901231276617</v>
+        <v>-4.91012974773578</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.797101907305283</v>
+        <v>-4.484702118812031</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.820574422643411</v>
+        <v>-4.86619453208138</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.678168142887067</v>
+        <v>-6.265284272502306</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.123128833506954</v>
+        <v>-8.239567463745871</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.36972596781135</v>
+        <v>-9.835361488904411</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-10.9704365985773</v>
+        <v>-10.41964996022276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08022</t>
+          <t>X ≈ -0.08028</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>157</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.62104341906938</v>
+        <v>-6.986408246465146</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-9.506114862451682</v>
+        <v>-10.14424432405558</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.716172871410542</v>
+        <v>-7.353268936574246</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-9.133718428458984</v>
+        <v>-9.771155595996362</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-9.03506530639573</v>
+        <v>-9.623462061789049</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.279092550645849</v>
+        <v>-4.892077816855618</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.09479581620249178</v>
+        <v>-0.4941351799659941</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.920043528220901</v>
+        <v>-3.507738640986425</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.617968359903202</v>
+        <v>-3.544711250123505</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.741772506551392</v>
+        <v>-5.642425181256669</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.583416339971109</v>
+        <v>-6.483508303952</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.8229235379344</v>
+        <v>-8.336169592064522</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-10.15390241672537</v>
+        <v>-10.64215554410634</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-11.20205211681702</v>
+        <v>-11.66699603240959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06319</t>
+          <t>X ≈ -0.06327</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.309645312302308</v>
+        <v>-3.059562374337659</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.815859029675522</v>
+        <v>-3.543838360592289</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.86808897796648</v>
+        <v>-5.585927997258644</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.080405270842334</v>
+        <v>-3.807692307692434</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7512915090206462</v>
+        <v>-0.4507876024903865</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.558889855076416</v>
+        <v>-1.276903182572681</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.196086402187646</v>
+        <v>-1.887009821248689</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.425585985201025</v>
+        <v>-5.100095328884784</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.724137202497161</v>
+        <v>-2.389815190768701</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.126542186672324</v>
+        <v>-3.763094321033989</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.331243344932517</v>
+        <v>-3.967234768570322</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.191892816886451</v>
+        <v>-2.810166932304334</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.612043670200116</v>
+        <v>-3.205324858868288</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6238770807470644</v>
+        <v>-0.209027249600048</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04616</t>
+          <t>X ≈ -0.04626</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.219938670320353</v>
+        <v>2.231267485457742</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.645013047973876</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.632784611304992</v>
+        <v>3.271593791297633</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.9088669950738009</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.797369774447048</v>
+        <v>2.481194208801774</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.804145513484038</v>
+        <v>4.909152141413905</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8732813080640227</v>
+        <v>0.9691857073607508</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.970315228379754</v>
+        <v>2.658525360770419</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9368207742968764</v>
+        <v>-1.257757593193858</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3500125661253009</v>
+        <v>0.07358623978406342</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.000012262565974</v>
+        <v>0.7315147577654102</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.461740842271723</v>
+        <v>1.220715977888922</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.896290843659266</v>
+        <v>1.687627016842335</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.549376921236224</v>
+        <v>2.367706361616314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02914</t>
+          <t>X ≈ -0.02924</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>319</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.637655842446577</v>
+        <v>-2.353372012974688</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.8005660734414377</v>
+        <v>-0.1747936122371883</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.762735577318814</v>
+        <v>-2.135929719674223</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.319030809905854</v>
+        <v>-1.69256605463503</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.28992224387936</v>
+        <v>-0.6144170764647612</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.500385204839887</v>
+        <v>-3.162948172065754</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.644656692632772</v>
+        <v>-2.283165389817931</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.857806841121629</v>
+        <v>-1.181600031079007</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.2918297499955</v>
+        <v>-0.5916133925669769</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.828268922500911</v>
+        <v>-1.101962349557361</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.032970080761103</v>
+        <v>-1.30610279709353</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-0.9344564359042522</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.791783534070291</v>
+        <v>-1.016134738643558</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.080569500452647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.0121</t>
+          <t>X ≈ -0.01222</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>347</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6077171832721078</v>
+        <v>-1.213281853705361</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.544785484470985</v>
+        <v>2.967229821945637</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.308199156768211</v>
+        <v>-0.8847214228531541</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1779740131798491</v>
+        <v>-0.754837381638545</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.59810794667893</v>
+        <v>-3.837746464953511</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.283442850761418</v>
+        <v>-1.547669879852293</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.520890962189036</v>
+        <v>-3.049248159279415</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3942996636126708</v>
+        <v>-0.9214209772995829</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6974559320258749</v>
+        <v>0.1943441657249494</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1524628643039136</v>
+        <v>-0.6294844150900332</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5073892915569189</v>
+        <v>0.03092845149490842</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.187339184329829</v>
+        <v>-1.64001143938227</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.274354342760283</v>
+        <v>0.8466750144573538</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.211905554946412</v>
+        <v>0.8075354384323816</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.004925</t>
+          <t>X ≈ 0.004792</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.138810767376462</v>
+        <v>-2.674046251116565</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.776312649914047</v>
+        <v>-2.290010221518244</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.513189297826905</v>
+        <v>-2.028010504914995</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.382964154238543</v>
+        <v>-1.898126463700237</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6186221283868676</v>
+        <v>-0.4201624898980612</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6655940065113839</v>
+        <v>0.8362295862979181</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.225620489350469</v>
+        <v>2.742786611826631</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.100657108721627</v>
+        <v>1.621216146525249</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2761145214853613</v>
+        <v>0.2727681275523963</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1391912125520562</v>
+        <v>0.4325461041143797</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.330734476075413</v>
+        <v>-0.7552009007988332</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.6144412464022082</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.374401913875744</v>
+        <v>-1.747929794915727</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.148666263649069</v>
+        <v>-1.49888493290036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.02195</t>
+          <t>X ≈ 0.0218</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.255926074728812</v>
+        <v>2.29415863774647</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.048248753594841</v>
+        <v>2.134469097074565</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1009085960725926</v>
+        <v>-0.3945002079659261</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.18721128435795</v>
+        <v>2.93823080833748</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.701553310209626</v>
+        <v>3.16072543962764</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.244541374932354</v>
+        <v>1.298279641720555</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.458076629701345</v>
+        <v>0.5258797802530566</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.692762371879596</v>
+        <v>0.7717907921117089</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.333534601321659</v>
+        <v>1.802433841337987</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.4836158049918</v>
+        <v>0.978605260523004</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.980669032696525</v>
+        <v>1.842080471349895</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.716801571016745</v>
+        <v>2.611990980956783</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.647527910685795</v>
+        <v>2.928576826634945</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.925895139859698</v>
+        <v>4.245237347013308</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.03897</t>
+          <t>X ≈ 0.03882</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>266</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.729036331286224</v>
+        <v>-2.134171975262923</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.219921672470321</v>
+        <v>-5.59704830853903</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.990632906849378</v>
+        <v>-5.614846447229809</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.619806259501658</v>
+        <v>-9.244360902255558</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-10.90997551184552</v>
+        <v>-10.48548974245564</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-10.61260148221043</v>
+        <v>-9.460824524388592</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.441672743732191</v>
+        <v>-7.265841515869738</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.532801537894997</v>
+        <v>-7.35573442662902</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.59378369441756</v>
+        <v>-8.144586735013931</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.180544596010705</v>
+        <v>-4.081197270716132</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.761185603894958</v>
+        <v>-5.037217417500301</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.223048053043399</v>
+        <v>-3.475291281639173</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.387559808612359</v>
+        <v>-1.99074996008278</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4099444591378401</v>
+        <v>-0.6138855491951958</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.056</t>
+          <t>X ≈ 0.05584</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.677814128195813</v>
+        <v>2.825856554559657</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.638056606560554</v>
+        <v>4.009477888376132</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.640110618630906</v>
+        <v>4.010996817057475</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.198907190790656</v>
+        <v>0.5835686053077396</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.644744621821985</v>
+        <v>2.465860966332052</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.132594841933269</v>
+        <v>3.529160319143116</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.238360673143241</v>
+        <v>4.654274980905804</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.787165045229571</v>
+        <v>2.607414552538266</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.546726528381711</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.860391076503909</v>
+        <v>4.513411781558816</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.655689918243759</v>
+        <v>4.309271334022682</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.69006807059904</v>
+        <v>4.367438071387575</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.66674261411103</v>
+        <v>4.367537061819895</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.4726011007417554</v>
+        <v>-0.5217579971134469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.07303</t>
+          <t>X ≈ 0.07286</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7658372162188911</v>
+        <v>0.4813411665660112</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.752053720557662</v>
+        <v>2.316967500213529</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.223083201603494</v>
+        <v>2.350579939249293</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.054607046490553</v>
+        <v>1.198412698412739</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5163174933948156</v>
+        <v>0.7091635574607196</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.216611507273036</v>
+        <v>-2.009503915173283</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.331624896842285</v>
+        <v>-5.061612995851739</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.201290943226432</v>
+        <v>-3.390693619482938</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.993874831350979</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.276694060581221</v>
+        <v>-6.388246946186911</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.914295651741902</v>
+        <v>-7.019737821073385</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.014116633585665</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-8.165869218500802</v>
+        <v>-8.211429864973219</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.507233135373838</v>
+        <v>-7.107684148256901</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.09006</t>
+          <t>X ≈ 0.08987</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.591547737581514</v>
+        <v>2.234413722558273</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.255723963358335</v>
+        <v>0.6512366374024978</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.658054027878663</v>
+        <v>6.096914707481787</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.512916852626525</v>
+        <v>6.956725755995826</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.249989618371409</v>
+        <v>5.737549607744718</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.098088285687496</v>
+        <v>5.280408119264301</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.636566332218585</v>
+        <v>8.139460059235915</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.270946963794181</v>
+        <v>4.753919269655498</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.833153213068421</v>
+        <v>8.366581697015043</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.809321373260303</v>
+        <v>5.352972094302423</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.706069490362502</v>
+        <v>2.229123617568995</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.740447642717825</v>
+        <v>1.557363347634698</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.320296789404338</v>
+        <v>1.162205421070965</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.546032439630871</v>
+        <v>1.411250283086162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.1071</t>
+          <t>X ≈ 0.1069</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6440839694657114</v>
+        <v>1.527155255858361</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.217102123598174</v>
+        <v>-2.540493878986936</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.361873508353256</v>
+        <v>-1.070877830034462</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.893351635235078</v>
+        <v>2.164596273291821</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.230062082139483</v>
+        <v>3.53870116960708</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.652436111774541</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10.9427257525083</v>
+        <v>11.20424674826887</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>11.72565710872156</v>
+        <v>11.98065001273026</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.539674952198894</v>
+        <v>8.838087341481653</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.689756155868984</v>
+        <v>8.0142587606666</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.235054997608735</v>
+        <v>6.567882288285936</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.394433149964051</v>
+        <v>5.383813000806036</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.974282296650706</v>
+        <v>4.98865507424221</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.200017946877239</v>
+        <v>5.237699936257613</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.1241</t>
+          <t>X ≈ 0.1239</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7.654219104600749</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.745735714239657</v>
+        <v>9.354986952026131</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>8.350964329484654</v>
+        <v>8.271593791297555</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.156865148748651</v>
+        <v>9.780788177339943</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.564521541598864</v>
+        <v>4.463952829491426</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.159192868531292</v>
+        <v>1.288462486241386</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.750158184940801</v>
+        <v>2.607116741843519</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.958765216829732</v>
+        <v>2.83093915387397</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.222107384631244</v>
+        <v>2.10431137232338</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.02083723695007933</v>
+        <v>0.5908276190945543</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.913593651039854</v>
+        <v>-4.440899035338042</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.87921549868453</v>
+        <v>-5.072387470386943</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.846855741778356</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.397955026095723</v>
+        <v>-4.528845362521572</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1411</t>
+          <t>X ≈ 0.1409</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5190839694657043</v>
+        <v>0.8879464275402</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.907897876401819</v>
+        <v>8.042633420054244</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>9.51312649164678</v>
+        <v>8.619769218147361</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.643351635235142</v>
+        <v>4.866158113730975</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>9.105062082139447</v>
+        <v>8.260404118410079</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10.40243611177453</v>
+        <v>11.44581099645231</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.317725752508373</v>
+        <v>0.7055432567414002</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1493428912784367</v>
+        <v>0.2397104963580574</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.789674952198844</v>
+        <v>3.115359246444619</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.939756155869048</v>
+        <v>3.262404452037401</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.735054997608799</v>
+        <v>2.087390218093546</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>4.087304528273918</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.349282296650713</v>
+        <v>2.721272815302321</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>0.05769631809439346</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.1582</t>
+          <t>X ≈ 0.1579</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>94</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.965892480103953</v>
+        <v>3.872866898517266</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1632170253379854</v>
+        <v>0.1620302388933297</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.295384146651095</v>
+        <v>-1.295537536655416</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.153989933107482</v>
+        <v>4.153495440729444</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.807189741713913</v>
+        <v>6.85573566147972</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.040733984114965</v>
+        <v>5.000861605830529</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.019853412082831</v>
+        <v>7.067865091073188</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.68044434276424</v>
+        <v>7.66586211792383</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.300313250071156</v>
+        <v>2.309740572616754</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.769543389911483</v>
+        <v>6.805060927972072</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.628672018885396</v>
+        <v>7.664750267669966</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.726879958474761</v>
+        <v>8.786746792268964</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.43438867962944</v>
+        <v>10.51924844017322</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.340975393685817</v>
+        <v>5.449144366018324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1752</t>
+          <t>X ≈ 0.1749</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>76</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.486845244822867</v>
+        <v>2.485658458378211</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7762843863836295</v>
+        <v>0.7761309963793082</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.22229900365619</v>
+        <v>2.221804511278158</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-7.526516865228935</v>
+        <v>-7.477970945463206</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.281774414541253</v>
+        <v>-3.25781700559164</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>-0.6868941474487116</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.376972898195341</v>
+        <v>6.742009934273277</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.631780215356784</v>
+        <v>8.020826798820693</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.466071945342676</v>
+        <v>5.881208744321462</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.945581313398264</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.77033492822966</v>
+        <v>11.91902447600749</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.31186005214028</v>
+        <v>13.48385881170714</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1922</t>
+          <t>X ≈ 0.192</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.259343709725428</v>
+        <v>7.746298431523314</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.245560214064156</v>
+        <v>8.727223910469981</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.253386231906518</v>
+        <v>5.769383358052714</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.682312674196176</v>
+        <v>7.181318681318679</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.04012701720435</v>
+        <v>10.53822338652058</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.740098449436836</v>
+        <v>8.246906341236937</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.759284194066808</v>
+        <v>3.058045123806373</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.59091684898133</v>
+        <v>3.874263645474322</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.529934692458632</v>
+        <v>3.837291036337554</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.576119792232625</v>
+        <v>6.859616301676382</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>11.26752253007633</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.704498085029023</v>
+        <v>9.277745155607725</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.07655502392345</v>
+        <v>16.57489492135161</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.70488807674742</v>
+        <v>14.25983721926442</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.2092</t>
+          <t>X ≈ 0.209</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.769083969465591</v>
+        <v>2.809037111283168</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>1.225860026127378</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.929793158313387</v>
+        <v>7.215100761216924</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>18.56001830190174</v>
+        <v>17.98328267477204</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.68839541547279</v>
+        <v>8.983395235947775</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.652436111774591</v>
+        <v>2.873202031362503</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>4.940205516605069</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.267323775388292</v>
+        <v>6.602032330689809</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.123008285532123</v>
+        <v>4.437400147084873</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.439756155869048</v>
+        <v>5.74123114073798</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>14.5683883309422</v>
+        <v>14.04772899107422</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>9.850576579503063</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.18261562998406</v>
+        <v>13.71073780187529</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>9.70446351495449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.2263</t>
+          <t>X ≈ 0.226</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>45</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.35234232084626</v>
+        <v>8.128933312179385</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.068682047202394</v>
+        <v>-1.153693565024241</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.68998169809813</v>
+        <v>-7.690476190476197</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.783826806749445</v>
+        <v>-3.735280886983695</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9579916673300559</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.762170196952809</v>
+        <v>7.587959653720908</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.072879330943849</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.234119396643294</v>
+        <v>7.085154284200769</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.60642282253559</v>
+        <v>10.70577014783026</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.62394388649763</v>
+        <v>12.7238519225164</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.213877594408594</v>
+        <v>8.33757421543681</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.16463851109527</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311064</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.2433</t>
+          <t>X ≈ 0.243</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>45</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>11.96352841391009</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.13012009862404</v>
+        <v>10.35115553440161</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>7.735195323864716</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.08779607967958</v>
+        <v>10.08730158730161</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.54950652658389</v>
+        <v>9.598052446349691</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.180213889552341</v>
+        <v>3.204171298501919</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>0.9212929870542794</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.567452729976623</v>
+        <v>2.640709839756354</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163629</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.95727721983102</v>
+        <v>6.057185255849731</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.65832203885305</v>
+        <v>12.78201865988125</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.68261562998404</v>
+        <v>16.83130517776187</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>16.90835128021055</v>
+        <v>17.08035003977724</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.2603</t>
+          <t>X ≈ 0.26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-12.94603230960414</v>
+        <v>-13.87374818852336</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-19.20838119336562</v>
+        <v>-20.00237981913375</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.30082699672531</v>
+        <v>-11.30520871653936</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.845020457788095</v>
+        <v>-6.629870129870149</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-10.70889140623265</v>
+        <v>-9.391846543549327</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.76035458589989</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-8.170646340514907</v>
+        <v>-6.906989841228636</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.96329637965047</v>
+        <v>-9.645549874339203</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-8.698697140824422</v>
+        <v>-7.409795210748776</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.571871751107771</v>
+        <v>-1.415441973381938</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4509915140191083</v>
+        <v>0.6531448518092944</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.067776152361482</v>
+        <v>-3.834142956280374</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.488817180371647</v>
+        <v>2.588880935337635</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.040134225947043</v>
+        <v>5.110653070080275</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.2773</t>
+          <t>X ≈ 0.277</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.630195080576797</v>
+        <v>6.313417586877769</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.57456454306845</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.068682047202294</v>
+        <v>-1.545850427769302</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.198907190790699</v>
+        <v>-1.415966386554672</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.216173193250562</v>
+        <v>3.977137413669929</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.513547222885649</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.428836863619516</v>
+        <v>4.189266843263439</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.961768219832742</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.900786063310001</v>
+        <v>3.6864614737433</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.060243844130966</v>
+        <v>-8.902072989424624</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-9.106213436960765</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.78612240559139</v>
+        <v>-14.93039964077229</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.20627325890489</v>
+        <v>-15.32555756733612</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.98053760867835</v>
+        <v>-15.07651270532075</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4047</v>
+        <v>4057</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1299214078892916</v>
+        <v>0.1434508286756753</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.08380327181940572</v>
+        <v>0.09692981691710401</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02273713728502003</v>
+        <v>0.03608027961689686</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01850568995537571</v>
+        <v>0.03184165232357827</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0379359454739685</v>
+        <v>-0.02592962721430325</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.05101810930844408</v>
+        <v>0.06353989218786893</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.04487908222277071</v>
+        <v>-0.03288461574540946</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01966771814674217</v>
+        <v>0.03158077251824665</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02769918403017613</v>
+        <v>-0.01643770660835742</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1481233800480695</v>
+        <v>-0.137207772222304</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3884017925146637</v>
+        <v>-0.3768596264710453</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.4143159238812686</v>
+        <v>-0.4034950134372934</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3513105887247718</v>
+        <v>-0.3413578746448991</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3587601603626851</v>
+        <v>-0.3496064140884982</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4019</v>
+        <v>4030</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0007573003756178309</v>
+        <v>0.0004001711555545739</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1128098089247658</v>
+        <v>0.1125497836731455</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1036972112497594</v>
+        <v>0.103421010575893</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.04891132746646321</v>
+        <v>0.04879773691654776</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.04547916257639173</v>
+        <v>0.04343221581955703</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1330047733091746</v>
+        <v>0.1316931740178617</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08672724282132549</v>
+        <v>0.08458806315585576</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1301602143116938</v>
+        <v>0.1278531349409135</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05806461422668008</v>
+        <v>0.05500145479143725</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.007546851836707447</v>
+        <v>-0.01146667253003386</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2977644951808571</v>
+        <v>-0.3009159646368502</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3489453628436294</v>
+        <v>-0.35290197503938</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3074341212597318</v>
+        <v>-0.3124970218577374</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.366260978228496</v>
+        <v>-0.3720899933079593</v>
       </c>
     </row>
     <row r="8">
@@ -2318,101 +2318,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3993</v>
+        <v>4004</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06526469837228888</v>
+        <v>0.0664378390413205</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1151388252158014</v>
+        <v>0.1148784206344544</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.08355606207634736</v>
+        <v>0.0833342473460732</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07752600445822821</v>
+        <v>0.0773364652288393</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.07757582526788553</v>
+        <v>0.07511311030292234</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1637457843563936</v>
+        <v>0.1621861428577418</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1177257525083704</v>
+        <v>0.1151764741314523</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1144730627101183</v>
+        <v>0.1118747459283114</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1173387841148141</v>
+        <v>0.1136180185762043</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0432310845613344</v>
+        <v>-0.04772286614181809</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3089890464352436</v>
+        <v>-0.3127784188307245</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3857608425264942</v>
+        <v>-0.3904448670505687</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3162159507203484</v>
+        <v>-0.3222528746725786</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4269855592584904</v>
+        <v>-0.4338024743752769</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1568</t>
+          <t>X &gt; -0.1569</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3965</v>
+        <v>3976</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.0831865335682167</v>
+        <v>0.08452342204207497</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1699044139929669</v>
+        <v>0.1694994550524456</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04028946951398638</v>
+        <v>0.04018654533446409</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0584459748577828</v>
+        <v>0.05831123216973566</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1377747142481525</v>
+        <v>0.1347874247408569</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1973014528266361</v>
+        <v>0.1954698259450325</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1012101432435131</v>
+        <v>0.09835103933198042</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1767714376060425</v>
+        <v>0.1736364641841561</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1045364131560262</v>
+        <v>0.1003096053093699</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02597828605593122</v>
+        <v>-0.03124827763040372</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3677675830363611</v>
+        <v>-0.3721241742136954</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3949227865118061</v>
+        <v>-0.400485110857808</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3471372696629587</v>
+        <v>-0.3541780172762614</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4098496445477267</v>
+        <v>-0.4179732331939121</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3927</v>
+        <v>3938</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1332971674351882</v>
+        <v>0.1347882004230669</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1856333422561036</v>
+        <v>0.185192102615396</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0005396525474381519</v>
+        <v>-0.0005065856129675694</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.04229564143778219</v>
+        <v>-0.04527722738284723</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.04030142308329943</v>
+        <v>0.038659106127092</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.07115737426738633</v>
+        <v>0.06789205760768624</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.101102061683747</v>
+        <v>0.09767343379282067</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.07960374161898898</v>
+        <v>0.07469975155500919</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.01852417992343192</v>
+        <v>-0.02482345947569797</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3870824069713521</v>
+        <v>-0.3923904299604501</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.4148376568569461</v>
+        <v>-0.4215910411903749</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3879885791130349</v>
+        <v>-0.3964175945153485</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4280378208843985</v>
+        <v>-0.4378487074717867</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3861</v>
+        <v>3864</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.02813725451479598</v>
+        <v>0.03051236907742094</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1640427664406232</v>
+        <v>0.1636770342296145</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.138639801583345</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.09829993090516354</v>
+        <v>-0.09797920200605148</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.07878048647784652</v>
+        <v>-0.08264296633645785</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.04033965207839429</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.004416586273251255</v>
+        <v>0.02861524085027156</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.04835894513648498</v>
+        <v>-0.009656052398867132</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.005767823565001606</v>
+        <v>0.0451496892724208</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1047803537115328</v>
+        <v>-0.04052423341761369</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.4648414291131076</v>
+        <v>-0.385362800352361</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5340365548520367</v>
+        <v>-0.442100441113169</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4363210176941905</v>
+        <v>-0.331264895545587</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4809261090668073</v>
+        <v>-0.3782420927279304</v>
       </c>
     </row>
     <row r="12">
@@ -2529,1242 +2529,1242 @@
         <v>3772</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1032345127998653</v>
+        <v>0.10616724488046</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.255723963358335</v>
+        <v>0.2551118301104793</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.006491748013871756</v>
+        <v>0.007949304709619298</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.0441999915447937</v>
+        <v>0.07290210450749868</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.04340027204931118</v>
+        <v>-0.005122156824931778</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1479292188795185</v>
+        <v>0.2027893926479365</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2222856676727289</v>
+        <v>0.2889772409216604</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2589285827407153</v>
+        <v>0.3407307235378951</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1979464262179391</v>
+        <v>0.2919574857073641</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1433616701850013</v>
+        <v>0.2510240109648976</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2734285654877056</v>
+        <v>-0.1501985985929863</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3185838171620787</v>
+        <v>-0.1832020604415021</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1820008422676267</v>
+        <v>-0.03331129448979908</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2478876734833051</v>
+        <v>-0.07588891391664276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.08873</t>
+          <t>X &gt; -0.08879</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2991442269293572</v>
+        <v>0.2684263629038739</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4956820451227202</v>
+        <v>0.479547891709629</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1283004165988473</v>
+        <v>0.1131921596928365</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.09418702280019886</v>
+        <v>0.07878266312000903</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02152332563437653</v>
+        <v>0.05503187923271469</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2093383303447851</v>
+        <v>0.2182883728599592</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4259152896214857</v>
+        <v>0.4588371029116161</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4792520142269723</v>
+        <v>0.5132672121887296</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.363490345241857</v>
+        <v>0.4489123467540068</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3078744796159114</v>
+        <v>0.4191691985786861</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.06116521603130565</v>
+        <v>0.05073521325507357</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.02678706367598238</v>
+        <v>0.08151969432205419</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1556367200963393</v>
+        <v>0.288771406312442</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1074748080111831</v>
+        <v>0.2639937053486179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0717</t>
+          <t>X &gt; -0.07178</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6100971348920936</v>
+        <v>0.5943230821230259</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9451045163560252</v>
+        <v>0.9567826207153871</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4358511625111205</v>
+        <v>0.4485954192390267</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5088353215545496</v>
+        <v>0.5212548538728754</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4284736448183324</v>
+        <v>0.4898025655675937</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4110222594562742</v>
+        <v>0.4478527481919556</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4407938692799789</v>
+        <v>0.5016458721281509</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6319965477599752</v>
+        <v>0.6938960874243492</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5423938989647397</v>
+        <v>0.628311174997144</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5797103630813538</v>
+        <v>0.6914639961850284</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2319067434588291</v>
+        <v>0.3442620321968519</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3235258803590924</v>
+        <v>0.4596533761425761</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6188873338573515</v>
+        <v>0.7798030318391227</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6156590459041453</v>
+        <v>0.799949467531178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05467</t>
+          <t>X &gt; -0.05476</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3313</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8242454545245081</v>
+        <v>0.7950496601718768</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.205211489441361</v>
+        <v>1.204024702996705</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7802559815350989</v>
+        <v>0.7801025915307775</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7595605093673541</v>
+        <v>0.7590660169893511</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4929280646326575</v>
+        <v>0.5414739843984293</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5186449859067466</v>
+        <v>0.5426023948563596</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5848552423966851</v>
+        <v>0.6328669213870057</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9629420468441765</v>
+        <v>1.012189609237893</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7208551514140638</v>
+        <v>0.7941122611937601</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8368282959233184</v>
+        <v>0.9361756212178918</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4812065219070121</v>
+        <v>0.5811145579256873</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5155846742623353</v>
+        <v>0.63928129529058</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8500368997294956</v>
+        <v>0.9987264475073232</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6833789489901321</v>
+        <v>0.8553777085567944</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03765</t>
+          <t>X &gt; -0.03775</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3079</v>
+        <v>3081</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7181745833013125</v>
+        <v>0.6869021316206485</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.315497746489505</v>
+        <v>1.343257665744247</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5634675114583985</v>
+        <v>0.5924927381241218</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8560830415358964</v>
+        <v>0.8846617517503574</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3177934884402021</v>
+        <v>0.3954126107984379</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1929525132035721</v>
+        <v>0.2138002068650096</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5629352361069309</v>
+        <v>0.6075420403919054</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8103842928723282</v>
+        <v>0.8882201531017202</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.846836368243018</v>
+        <v>0.9486185274118526</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8738256589544093</v>
+        <v>1.001128797619266</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4417779596094462</v>
+        <v>0.5697893887069867</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4436780346669522</v>
+        <v>0.5954991315895697</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7705229592034897</v>
+        <v>0.9468520781189014</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.541565527260488</v>
+        <v>0.7414990173819191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02062</t>
+          <t>X &gt; -0.02073</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2760</v>
+        <v>2762</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.106040491204773</v>
+        <v>1.038041687060876</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.560071789445296</v>
+        <v>1.518586542527764</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9479091003424358</v>
+        <v>0.907614665726463</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.223061780162681</v>
+        <v>1.182321299265539</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5036128067771344</v>
+        <v>0.5120439179081231</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6198274161223623</v>
+        <v>0.603801196321534</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9336677814938739</v>
+        <v>0.9414072359881871</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.118773050750612</v>
+        <v>1.127276141064662</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.094022778285805</v>
+        <v>1.126509180008966</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.186132967463195</v>
+        <v>1.2440274493026</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7278086207972052</v>
+        <v>0.7864474651987905</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6897230050365835</v>
+        <v>0.772202906401489</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.066673600998541</v>
+        <v>1.173569237621876</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8213947584714489</v>
+        <v>0.9519406745829428</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00359</t>
+          <t>X &gt; -0.003716</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.352486373112562</v>
+        <v>1.361523785879058</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.274661241507495</v>
+        <v>1.310437798031693</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.128542985637665</v>
+        <v>1.165147014685935</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.424536881816167</v>
+        <v>1.460662525879918</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.093458269458139</v>
+        <v>1.137044854907288</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8935260413228079</v>
+        <v>0.9129359637883283</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.430448504269656</v>
+        <v>1.514805754480051</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.33635955381073</v>
+        <v>1.421643801550125</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.151050832845357</v>
+        <v>1.260447589928866</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.378628928351375</v>
+        <v>1.513223563979302</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7595058886158483</v>
+        <v>0.8950044414949616</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.959652793561304</v>
+        <v>1.118802648839157</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.036808198018299</v>
+        <v>1.220539132213219</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7652375904744275</v>
+        <v>0.9726895842906984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01344</t>
+          <t>X &gt; 0.0133</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.999880555525394</v>
+        <v>1.944864478430553</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.858585406036724</v>
+        <v>1.830881706070905</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.653477368839759</v>
+        <v>1.626717177471846</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.97336585998621</v>
+        <v>1.946174678402166</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.340244633111475</v>
+        <v>1.362138807592423</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9263811094037351</v>
+        <v>0.9240238524777027</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.315829119032784</v>
+        <v>1.337301412541336</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.370334681030776</v>
+        <v>1.392795666376003</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.356768361397528</v>
+        <v>1.403216422168121</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.59741381352665</v>
+        <v>1.669435234718065</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.060801797039808</v>
+        <v>1.133541232679605</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.095179949395131</v>
+        <v>1.191707970044497</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.52851416009311</v>
+        <v>1.649630612201051</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.185259767645384</v>
+        <v>1.329955095069501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.03046</t>
+          <t>X &gt; 0.03031</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1824</v>
+        <v>1829</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.95987344314986</v>
+        <v>1.891200367567912</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.828950507980771</v>
+        <v>1.784239794167121</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.927600175857314</v>
+        <v>1.937248662057982</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.783702512428121</v>
+        <v>1.793759275169883</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9712901523148858</v>
+        <v>1.085811391735724</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7204185679148836</v>
+        <v>0.8665247399696412</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.293602945490825</v>
+        <v>1.461964878190869</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.319955354335654</v>
+        <v>1.488204288392545</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.204148636409386</v>
+        <v>1.341882308014632</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.615194752360217</v>
+        <v>1.77557149647248</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.9170725414684497</v>
+        <v>1.02468419273081</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8418015710167523</v>
+        <v>0.9735015588545863</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.353668261563001</v>
+        <v>1.453138602219681</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7570354907368966</v>
+        <v>0.882063179926682</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.04749</t>
+          <t>X &gt; 0.04733</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.589687307077973</v>
+        <v>2.576260535957545</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.032416490009005</v>
+        <v>3.040428300449804</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.27949362900236</v>
+        <v>3.222506051098634</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.730643034464919</v>
+        <v>3.672287725070831</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.999798924244715</v>
+        <v>3.055079531015899</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.655324430131401</v>
+        <v>2.624090257768295</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.955723185114266</v>
+        <v>2.94731132785185</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.002133360326248</v>
+        <v>2.993314779880542</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.876966351428628</v>
+        <v>2.956342170743746</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.604711226472332</v>
+        <v>2.772308855443796</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.886531249213419</v>
+        <v>2.056332195495671</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.535800287319702</v>
+        <v>1.73062177355154</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.821682810129531</v>
+        <v>2.039238639054268</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9562759699837997</v>
+        <v>1.136652023142567</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.06452</t>
+          <t>X &gt; 0.06435</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.572682744350793</v>
+        <v>2.528056114044311</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.722599254656025</v>
+        <v>2.85327597545335</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.016954975567153</v>
+        <v>3.070225010039401</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.219155616858416</v>
+        <v>4.268811341330427</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.068308636503914</v>
+        <v>3.168875177477737</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.370276846843446</v>
+        <v>2.449294284082924</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.515275522799335</v>
+        <v>2.617645828445248</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.043612698308152</v>
+        <v>3.067843602413056</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.599782149748613</v>
+        <v>2.649191603963281</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.362420780677567</v>
+        <v>2.436050046049061</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.545162195158561</v>
+        <v>1.621222575612208</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.12012227706979</v>
+        <v>1.221374045801525</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.465668207829886</v>
+        <v>1.589574897863656</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.231985787612317</v>
+        <v>1.456940370566052</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.08155</t>
+          <t>X &gt; 0.08136</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.960944434581926</v>
+        <v>2.973159550577698</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.931153690355309</v>
+        <v>2.969908115979472</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.187545096297946</v>
+        <v>3.22672774848261</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.899165588723513</v>
+        <v>4.936537440254902</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.616689989116196</v>
+        <v>3.703793875511174</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.355924483867554</v>
+        <v>3.418958576486226</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.201446682740922</v>
+        <v>4.287670517000542</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.385540829651859</v>
+        <v>4.472395377435049</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.231535417315129</v>
+        <v>4.342485965324272</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.218825923310852</v>
+        <v>4.355088611275093</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.362961974352984</v>
+        <v>3.500390542921153</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.653154080196678</v>
+        <v>2.815062856494222</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.535328808278621</v>
+        <v>3.721020171566096</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.109901667807478</v>
+        <v>3.319507412763613</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.09857</t>
+          <t>X &gt; 0.09838</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.015348643958717</v>
+        <v>3.08094248821206</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.325187097319642</v>
+        <v>3.308202037773988</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.823692126652119</v>
+        <v>2.807967776828832</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.661494644840261</v>
+        <v>4.641792180130828</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.376139990357167</v>
+        <v>3.407069130765713</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.246619676342306</v>
+        <v>3.147373286432348</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.695527246638562</v>
+        <v>3.725694832989632</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.402418047889178</v>
+        <v>4.431321071541326</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.701094375891486</v>
+        <v>3.755370826621785</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.131858610511465</v>
+        <v>4.209497517372291</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.606986694513807</v>
+        <v>3.685868251944839</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.787576159569241</v>
+        <v>2.998561080896522</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.861555509030651</v>
+        <v>4.094350971159102</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.340226057869778</v>
+        <v>3.597921924761273</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.1156</t>
+          <t>X &gt; 0.1154</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.503639954021629</v>
+        <v>3.402484576141298</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.466456434960378</v>
+        <v>4.518536282759221</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.685584664104958</v>
+        <v>3.610659476963789</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.231511223394726</v>
+        <v>5.154425266250463</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.406220383297743</v>
+        <v>3.379829081596739</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.495802261084044</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.203182637965256</v>
+        <v>2.17807676311822</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.894415152479667</v>
+        <v>2.8690563420665</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.704732867256759</v>
+        <v>2.703549028559529</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.399215615328451</v>
+        <v>3.4221369001867</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.065814328368127</v>
+        <v>3.089461748280435</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.456691837222813</v>
+        <v>2.504954963794425</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.838342785711198</v>
+        <v>3.909282898413117</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.16317753503683</v>
+        <v>3.258584829837233</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1326</t>
+          <t>X &gt; 0.1324</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.527033095061839</v>
+        <v>2.466191492648562</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.459567192777016</v>
+        <v>3.410660537034573</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.587848272250909</v>
+        <v>2.542988899430775</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.307898535076163</v>
+        <v>4.094673888512744</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.133678934285712</v>
+        <v>3.131491098271731</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.636140404302353</v>
+        <v>2.772365084705193</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.074482509265124</v>
+        <v>2.079797463094266</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.879273960867891</v>
+        <v>2.877787767481855</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.818291804345115</v>
+        <v>2.840815158345059</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.194128174946897</v>
+        <v>4.070699057782846</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.943322088228825</v>
+        <v>4.814425908824951</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.182787680965717</v>
+        <v>4.240681113804378</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.306357018431314</v>
+        <v>6.373169316782416</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.942267549420961</v>
+        <v>5.042435347834115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.1497</t>
+          <t>X &gt; 0.1494</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.906607598955247</v>
+        <v>2.772907043037542</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>2.510484674862823</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.278721954784778</v>
+        <v>1.362029705416042</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.866414017087692</v>
+        <v>3.944743935309965</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.00487304622262</v>
+        <v>2.134740077376918</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.168031574912533</v>
+        <v>1.086770879214711</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.217536716591539</v>
+        <v>2.346869506970386</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.451791324222576</v>
+        <v>3.39047070885119</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.823701417227205</v>
+        <v>2.787460363865335</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.242213622787702</v>
+        <v>4.227782726446584</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.360763882296887</v>
+        <v>5.344396995891621</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.260926533707035</v>
+        <v>4.270488261558405</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.054386266404961</v>
+        <v>7.0828775048059</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.956870498862116</v>
+        <v>6.011167649840132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.1667</t>
+          <t>X &gt; 0.1664</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.461612705097828</v>
+        <v>2.535759734746044</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.91939212927538</v>
+        <v>3.016802833076426</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.834965572106547</v>
+        <v>1.93499145026631</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.804271175465026</v>
+        <v>3.899737876802085</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9671310476566859</v>
+        <v>1.116910754198791</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1150797899354572</v>
+        <v>0.2429072821920357</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.179794718025605</v>
+        <v>1.329040183792259</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.321921476537717</v>
+        <v>2.468712010564893</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.720709434957477</v>
+        <v>2.890454997758368</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.479986040926462</v>
+        <v>3.672131004099342</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.654595227493857</v>
+        <v>4.844137345554081</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.079777977550329</v>
+        <v>3.296799495763011</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.107902986305888</v>
+        <v>6.34200854167625</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.873868521589884</v>
+        <v>6.132337807361345</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1837</t>
+          <t>X &gt; 0.1835</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.950838844117456</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.010961943254188</v>
+        <v>3.128933312179385</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.059087494432298</v>
+        <v>2.179639768309123</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.139173362254645</v>
+        <v>4.253968253968253</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.76522921305866</v>
+        <v>2.931385779682991</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.8341909864263428</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.863686755293884</v>
+        <v>1.754626320387572</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.675169643540563</v>
+        <v>1.566571337782008</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.89273901905122</v>
+        <v>1.80737650642299</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.271232478988772</v>
+        <v>3.205770147830229</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.016392044962558</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.265254876983626</v>
+        <v>2.504240882103481</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.909170876037905</v>
+        <v>5.164638511095212</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.299251930164161</v>
+        <v>4.580350039777237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.2007</t>
+          <t>X &gt; 0.2005</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>282</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.774403118401814</v>
+        <v>1.745207324049183</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.581656741650043</v>
+        <v>1.580469955205388</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.186885356895004</v>
+        <v>1.186731966890683</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.444770074951457</v>
+        <v>3.444275582573454</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.7788209473876719</v>
+        <v>0.8273668671534438</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.051464597445317</v>
+        <v>-1.027507188495704</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.346094546834607</v>
+        <v>1.394106225824927</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.879025903047868</v>
+        <v>0.9282734654415847</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.172653675603101</v>
+        <v>1.245910785382797</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.095784524663316</v>
+        <v>2.195131849957889</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.309523082715181</v>
+        <v>3.409431118733856</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.5070218024463955</v>
+        <v>0.6307184234746401</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.859920594523054</v>
+        <v>2.008610142300881</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.73104631567157</v>
+        <v>1.903045075238232</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.2178</t>
+          <t>X &gt; 0.2175</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.532441366602377</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.890803859307802</v>
+        <v>1.651391941020997</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2139811925014854</v>
+        <v>-0.01894179197456225</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3442063360898473</v>
+        <v>0.5364741641337361</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.048784071706706</v>
+        <v>-0.8038388066054196</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.606110896772471</v>
+        <v>-1.807649032467346</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>0.6848863676689021</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.02113776307324144</v>
+        <v>-0.2064783076080587</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.7725809351048341</v>
+        <v>0.6076129130423809</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.204713420826252</v>
+        <v>1.485911991801871</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.000012262566059</v>
+        <v>1.28177154426578</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.529712149181172</v>
+        <v>-1.213253207731036</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6678117204433036</v>
+        <v>-0.3318153896140075</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.01472564286634537</v>
+        <v>0.3427613872949777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.2348</t>
+          <t>X &gt; 0.2345</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.487337937719616</v>
+        <v>1.700414490902489</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1238481553442128</v>
+        <v>0.1172374057466357</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.01048098900128025</v>
+        <v>0.2498152069056232</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.257108248991756</v>
+        <v>2.484962406015029</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3975834205060522</v>
+        <v>-0.1095498928316161</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.216611507273079</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.24312080833819</v>
+        <v>-0.9500520421855256</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.710189452124929</v>
+        <v>-1.415884802568868</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.242071079547181</v>
+        <v>-0.92654162223198</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.033788817675983</v>
+        <v>-0.6977386240995855</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.767590505036701</v>
+        <v>-1.428194861109361</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.849614469083491</v>
+        <v>-3.475291281639215</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.211564264195843</v>
+        <v>-2.817817629255671</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.456728084868786</v>
+        <v>-2.042456977766619</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.2518</t>
+          <t>X &gt; 0.2515</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.78647158608991</v>
+        <v>-2.165284238680087</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.703213234709295</v>
+        <v>-3.058806151422147</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.709095730575442</v>
+        <v>-2.073233794909264</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1899816980981939</v>
+        <v>0.12561576354679</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.506049028971667</v>
+        <v>-3.122254067060297</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.903119443781023</v>
+        <v>-3.539123720655162</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.904496469713855</v>
+        <v>-1.530814292639249</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.760454002389487</v>
+        <v>-3.375957397850172</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.43254727002337</v>
+        <v>-2.033619662159388</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.588021621908787</v>
+        <v>-2.167793070560577</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.181611669057865</v>
+        <v>-3.751243862924248</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.008344627813656</v>
+        <v>-8.520663332455911</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.428495481127065</v>
+        <v>-8.915821259019737</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-8.508315386456083</v>
+        <v>-7.977121224590576</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2688</t>
+          <t>X &gt; 0.2685</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.9646285239211</v>
+        <v>2.935432729568468</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.323739460560233</v>
+        <v>4.322552674115578</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.948770056003212</v>
+        <v>1.948616665998891</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.069094209492562</v>
+        <v>3.068599717114559</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4394923733060949</v>
+        <v>-0.3909464535403231</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.112415373373977</v>
+        <v>-3.088457964424364</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7632703069638183</v>
+        <v>0.8112819859541389</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6938973467239151</v>
+        <v>-0.6446497843301984</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2352195066543032</v>
+        <v>0.3084766164339996</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.594897309477538</v>
+        <v>-2.495549984182965</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-5.769895497440707</v>
+        <v>-5.669987461422032</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.68601239459033</v>
+        <v>-10.56231577356208</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-14.07646027760671</v>
+        <v>-13.92777072982889</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-13.85072462738018</v>
+        <v>-13.67872586781352</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2859</t>
+          <t>X &gt; 0.2855</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.534403900498212</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.139632515743173</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.474676936439955</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.882889725089463</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.199973526779686</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4654067776121167</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-2.137294698507283</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.9934575779216317</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.843376374251491</v>
+        <v>-1.198991756931669</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.662535363836987</v>
+        <v>-4.974560775896336</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-10.44743431991539</v>
+        <v>-9.678298800436202</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-14.4820430045541</v>
+        <v>-13.6448852984286</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-14.25630735432757</v>
+        <v>-13.39584043641324</v>
       </c>
     </row>
   </sheetData>
@@ -3908,49 +3908,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.083325669088573</v>
+        <v>-3.700588015363174</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.080053930827091</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.47482531558213</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.139780894885341</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.141206660452703</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3806964183459485</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.763508885038483</v>
+        <v>6.080023145784395</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.681982409926441</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.44027736183741</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.20481639683285</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>20.84348873254856</v>
+        <v>20.02543922410366</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>20.87786688490389</v>
+        <v>20.08360596146856</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.25289675448204</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>18.27381312760013</v>
+        <v>17.55654051596772</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.474038924420604</v>
+        <v>2.444843130067973</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.839849871345933</v>
+        <v>-1.841036657790589</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.036423057902773</v>
+        <v>-4.036576447907095</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.203495211611703</v>
+        <v>-1.203989703989706</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.0600170370944042</v>
+        <v>0.108562956860176</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.246212536874118</v>
+        <v>-3.222255127924505</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2726807074633228</v>
+        <v>0.3206923864536435</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.996189738125217</v>
+        <v>-1.9469421757315</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.44733260985651</v>
+        <v>2.520589719636206</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.498314714427551</v>
+        <v>2.597662039722124</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.20352346607727</v>
+        <v>12.30343150209595</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.13880251933349</v>
+        <v>13.26249914036173</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>12.71865166602008</v>
+        <v>12.86734121379791</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.84528821714752</v>
+        <v>14.01728697671418</v>
       </c>
     </row>
     <row r="8">
@@ -4015,98 +4015,98 @@
         <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.07382849501309607</v>
+        <v>0.04463270066046476</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.537357598050733</v>
+        <v>-1.538544384495388</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.662055990105038</v>
+        <v>-2.66220938010936</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.80190383921741</v>
+        <v>-1.802398331595413</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.88033937771457</v>
+        <v>-0.8317934579487982</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.502673377276558</v>
+        <v>-3.478715968326945</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6676757073456514</v>
+        <v>-0.6196640283553307</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.13474435113239</v>
+        <v>-1.085496788738674</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2641275069433746</v>
+        <v>0.337384616723071</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.063843747109871</v>
+        <v>3.163191072404445</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.15841266184238</v>
+        <v>10.25832069786105</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.65264482879623</v>
+        <v>11.77634144982448</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.50256696818356</v>
+        <v>10.65125651596139</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>12.91808364030791</v>
+        <v>13.09008239987457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1568</t>
+          <t>X &lt; -0.1569</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>165</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3597039093222278</v>
+        <v>-0.3888997036748592</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.576950608446666</v>
+        <v>-2.578137394891321</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.167665190587833</v>
+        <v>-2.119119270822061</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.688472979134559</v>
+        <v>-3.664515570184946</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.422070164005653</v>
+        <v>-2.372822601611936</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.547250709774616</v>
+        <v>0.6205078195543123</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.121574337687171</v>
+        <v>2.220921662981745</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>9.795661058214861</v>
+        <v>9.895569094233537</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.830039210570185</v>
+        <v>9.953735831598429</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.409888357256776</v>
+        <v>9.558577905034603</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>203</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.249388936938288</v>
+        <v>-1.27858473129092</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.367964192563697</v>
+        <v>-2.369150979008353</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.284903065003462</v>
+        <v>-1.285056455007783</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3231545909001667</v>
+        <v>0.3226600985221637</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.755308387558166</v>
+        <v>1.803854307323938</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.08223906743955922</v>
+        <v>0.1061964763891723</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.5381512246021316</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.4695399356133478</v>
+        <v>-0.4202923732196311</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.9473104201791429</v>
+        <v>1.020567529958839</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.575224136164557</v>
+        <v>1.674571461459131</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.267074702042294</v>
+        <v>8.366982738060969</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>8.301452854397617</v>
+        <v>8.425149475425862</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.373912838522628</v>
+        <v>8.522602386300456</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.59964848874916</v>
+        <v>8.771647248315823</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.5876760272273813</v>
+        <v>0.55848023287475</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.384520896161355</v>
+        <v>-1.385707682606011</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.830816022332705</v>
+        <v>1.830662632328384</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.600030335596152</v>
+        <v>1.599535843218149</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.783762443150273</v>
+        <v>1.832308362916045</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.199537561049901</v>
+        <v>1.02206139076025</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.317725752508373</v>
+        <v>0.9614053015347892</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.784963678064692</v>
+        <v>1.217594201801269</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.180621592664473</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.395638508810173</v>
+        <v>1.43982550282422</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.203689683955659</v>
+        <v>5.928825849511959</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.843507224038198</v>
+        <v>6.348003417201753</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.918055530851461</v>
+        <v>5.230823829988111</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.143791181077994</v>
+        <v>5.479868692003478</v>
       </c>
     </row>
     <row r="12">
@@ -4220,1245 +4220,1245 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3187538683721911</v>
+        <v>-0.3479496627248224</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.92993996143602</v>
+        <v>-1.931126747880676</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.01532879290606814</v>
+        <v>-0.1627025740332186</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2805614082431163</v>
+        <v>-0.5733590733590859</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9633727088424493</v>
+        <v>0.5590134073106228</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.04565131991945</v>
+        <v>-1.600633506302877</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.257616713245056</v>
+        <v>-1.931559865798619</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.852639594575074</v>
+        <v>-2.667662896452228</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-1.623554424507944</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.8116250596006154</v>
+        <v>-1.906842464782379</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.291841701209904</v>
+        <v>1.943071141735579</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.491655372186344</v>
+        <v>2.001237879100472</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.402207087737061</v>
+        <v>0.7952691417258393</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.79289504184932</v>
+        <v>0.928588522162066</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.08873</t>
+          <t>X &lt; -0.08879</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.667907900453045</v>
+        <v>-1.412307433669426</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.175605178588</v>
+        <v>-2.995484518825279</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.017485753251179</v>
+        <v>-0.88702689835754</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5734172809202747</v>
+        <v>-0.4493272258803387</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2280129018115815</v>
+        <v>-0.0271148896610427</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.209473539149485</v>
+        <v>-1.253686962173234</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.418899761894934</v>
+        <v>-2.618133536243249</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.984394437670119</v>
+        <v>-3.180903409692739</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.697928353586271</v>
+        <v>-2.303059840855454</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.815937425911549</v>
+        <v>-2.614040535063609</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7889969063224882</v>
+        <v>-0.067475990762766</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3182896988206707</v>
+        <v>-0.5060555650565206</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8173843700159509</v>
+        <v>-1.808150604551052</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6838547044797494</v>
+        <v>-1.856255277196176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0717</t>
+          <t>X &lt; -0.07178</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.86612404286101</v>
+        <v>-2.737729427314903</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.709386074215466</v>
+        <v>-4.701191645605149</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.400320185323856</v>
+        <v>-2.432232377809598</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.653861987055883</v>
+        <v>-2.680313588850183</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.026720863596985</v>
+        <v>-2.327308028629126</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.957812335430432</v>
+        <v>-2.127123298847714</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.805135833805792</v>
+        <v>-2.107463181058748</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.96865753302292</v>
+        <v>-3.259604531338645</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.168203362933752</v>
+        <v>-2.602505726039894</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.778993844131008</v>
+        <v>-3.345511903451815</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.022378492219062</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-2.403166525303924</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.118535599738614</v>
+        <v>-3.951796316313349</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.280327965072438</v>
+        <v>-4.240599392627296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05467</t>
+          <t>X &lt; -0.05476</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.962843741377725</v>
+        <v>-2.807376985410173</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.514297539762232</v>
+        <v>-4.450431767185691</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.158371092894285</v>
+        <v>-3.116347518142994</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.966080045538746</v>
+        <v>-2.925161950221622</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.747238159991305</v>
+        <v>-1.919271329038629</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.870291160952746</v>
+        <v>-1.942027531907435</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.891012111569296</v>
+        <v>-2.059412269100115</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.509002672566339</v>
+        <v>-3.661246408021341</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.290617018604074</v>
+        <v>-2.556035525056267</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.076078192486676</v>
+        <v>-3.436858057297975</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.752749880439978</v>
+        <v>-2.133749361077697</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.018112637581666</v>
+        <v>-2.49241239768233</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.227734818263706</v>
+        <v>-3.787914765945395</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.691811918483836</v>
+        <v>-3.354432568918412</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03765</t>
+          <t>X &lt; -0.03775</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1051</v>
+        <v>1060</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.82302129369225</v>
+        <v>-1.717940343060327</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.574698548809849</v>
+        <v>-3.626870999595077</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.662014751291075</v>
+        <v>-1.732591790981253</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.424508873718679</v>
+        <v>-2.487983978638191</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7439945216341357</v>
+        <v>-0.9642591636700786</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3954864566862781</v>
+        <v>-0.4537562920099347</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.279627744656096</v>
+        <v>-1.400897994930553</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.074603061571658</v>
+        <v>-2.285836417064765</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.99062807810418</v>
+        <v>-2.273218172763229</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.31616801474712</v>
+        <v>-2.671422834625901</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.141605343947177</v>
+        <v>-1.508404793277514</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.244811864280891</v>
+        <v>-1.681258176276934</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.087980060763741</v>
+        <v>-2.590623820038935</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.524886905644166</v>
+        <v>-2.102039897329675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02062</t>
+          <t>X &lt; -0.02073</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1370</v>
+        <v>1379</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.010923261192346</v>
+        <v>-1.863560100749048</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.934359721282696</v>
+        <v>-2.835201203356995</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.916272494595077</v>
+        <v>-1.82515639476042</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.400126625634421</v>
+        <v>-2.305307004011119</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.8702823703623608</v>
+        <v>-0.8838559750400279</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.114254744538968</v>
+        <v>-1.07685089167672</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.595854494405209</v>
+        <v>-1.603959538198282</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.024342891278373</v>
+        <v>-2.031503271122922</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.828506865982966</v>
+        <v>-1.885622851316249</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.202893043548769</v>
+        <v>-2.309414233948502</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.348703196127545</v>
+        <v>-1.461708456965866</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.347184925837631</v>
+        <v>-1.508752922707849</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.019061977601659</v>
+        <v>-2.226665836730881</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.607463804947578</v>
+        <v>-1.865746165202211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00359</t>
+          <t>X &lt; -0.003716</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.729470943829149</v>
+        <v>-1.733803601770255</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.63403387605625</v>
+        <v>-1.676718139041689</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.593354989834694</v>
+        <v>-1.637285965715058</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.953637363027738</v>
+        <v>-1.995391705069132</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.418692263167621</v>
+        <v>-1.474634073022735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.148288525906629</v>
+        <v>-1.171068993693382</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.782042228930145</v>
+        <v>-1.893350854710199</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.696063727029973</v>
+        <v>-1.80910225729113</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.319500425269212</v>
+        <v>-1.468668169101761</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.789471037623173</v>
+        <v>-1.972457212478055</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9742473279725914</v>
+        <v>-1.162145121375424</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.314918217109764</v>
+        <v>-1.535110969748381</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.353860893104823</v>
+        <v>-1.609150332757338</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.037678616896777</v>
+        <v>-1.328301949407773</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01344</t>
+          <t>X &lt; 0.0133</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.94010973751567</v>
+        <v>-1.874103997098331</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.804841917006932</v>
+        <v>-1.768276673136327</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.730967996542198</v>
+        <v>-1.695645899336974</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.017898980225219</v>
+        <v>-1.980856722894941</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.298878804560069</v>
+        <v>-1.316980233388897</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8765190385458226</v>
+        <v>-0.8708109912915489</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.181288054197751</v>
+        <v>-1.199522627382564</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.276624588367667</v>
+        <v>-1.295480699527758</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.162941039903814</v>
+        <v>-1.207794853542083</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.541725325612489</v>
+        <v>-1.612002169942087</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.027790852193569</v>
+        <v>-1.101123495379404</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.114402737331979</v>
+        <v>-1.212625270817767</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.507295349244444</v>
+        <v>-1.62998091147697</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.204794027392921</v>
+        <v>-1.353918793309909</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.03046</t>
+          <t>X &lt; 0.03031</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2306</v>
+        <v>2312</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.424426164212669</v>
+        <v>-1.370326878650431</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.331101260785417</v>
+        <v>-1.296387016755396</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.530464358590592</v>
+        <v>-1.538253760174157</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.377373753365895</v>
+        <v>-1.385566629752681</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6832748509059101</v>
+        <v>-0.7748711019293353</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4921187715443907</v>
+        <v>-0.608089237896543</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8560745068950055</v>
+        <v>-0.9904505805754837</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.910588566018852</v>
+        <v>-1.044875311628402</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7317443468059111</v>
+        <v>-0.8427218007750099</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.168468952356115</v>
+        <v>-1.297684083603272</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6564564792209922</v>
+        <v>-0.7438706596770572</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6413120840046815</v>
+        <v>-0.7481839714449734</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9940206942465579</v>
+        <v>-1.076174286137821</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5706889048139914</v>
+        <v>-0.6733985184695825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.04749</t>
+          <t>X &lt; 0.04733</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2572</v>
+        <v>2578</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.455770962836091</v>
+        <v>-1.448745557036737</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.731421009047089</v>
+        <v>-1.738076554830485</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.989777108817798</v>
+        <v>-1.957092560775465</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.226516683897316</v>
+        <v>-2.193309781408708</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.737247100347957</v>
+        <v>-1.773334402424119</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.535548384349497</v>
+        <v>-1.518695419724416</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.63845881515352</v>
+        <v>-1.636196804478111</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.697054295467666</v>
+        <v>-1.694522573466706</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.543270333016515</v>
+        <v>-1.594675371238637</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.479498502516094</v>
+        <v>-1.584444156326747</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.080478982973723</v>
+        <v>-1.186346536306658</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9081115275805587</v>
+        <v>-1.029350849162668</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.034705266505135</v>
+        <v>-1.170504309119345</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.554064479250286</v>
+        <v>-0.6672579250533772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.06452</t>
+          <t>X &lt; 0.06435</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2824</v>
+        <v>2831</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.088600203956979</v>
+        <v>-1.068480319964337</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.165444859846417</v>
+        <v>-1.226598793968272</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.400453755266795</v>
+        <v>-1.425802408561623</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.921927122704169</v>
+        <v>-1.94602001307387</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.347461744193069</v>
+        <v>-1.395687772742676</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.031179707434504</v>
+        <v>-1.068851283784483</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.026322287053624</v>
+        <v>-1.075418311982638</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.297752785271307</v>
+        <v>-1.310881370477887</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.021565768904011</v>
+        <v>-1.046799954946692</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.003666757850951</v>
+        <v>-1.040261598201511</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6582948432118627</v>
+        <v>-0.6957356255115457</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4980827736027607</v>
+        <v>-0.5473926434093315</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6153194732607901</v>
+        <v>-0.6757569691307808</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5467950842842271</v>
+        <v>-0.6542549290205955</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.08155</t>
+          <t>X &lt; 0.08136</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3055</v>
+        <v>3065</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9489733968968039</v>
+        <v>-0.9506576338538437</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9457049928515247</v>
+        <v>-0.9571173143327343</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.127447546187533</v>
+        <v>-1.138522346992133</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.697594531159638</v>
+        <v>-1.706736353077822</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.206948361724777</v>
+        <v>-1.235461614230104</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.120580538568262</v>
+        <v>-1.140479242048393</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.351118140372108</v>
+        <v>-1.379054235167978</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.441404309115676</v>
+        <v>-1.469356155976804</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.321436158912263</v>
+        <v>-1.358566309356952</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.401858750963306</v>
+        <v>-1.448025876933535</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.130870443856203</v>
+        <v>-1.178074776020509</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9148978935425873</v>
+        <v>-0.9715588498097176</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.186058017485415</v>
+        <v>-1.250886603060039</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.073099892729957</v>
+        <v>-1.146947404485942</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.09857</t>
+          <t>X &lt; 0.09838</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3193</v>
+        <v>3202</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7965741715200068</v>
+        <v>-0.8149329757423516</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8939741984811818</v>
+        <v>-0.8885596007708969</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.8351881150947875</v>
+        <v>-0.8300085354568196</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.343847865233172</v>
+        <v>-1.337217576943608</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.9286668372859097</v>
+        <v>-0.9379522596955283</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8955957532676422</v>
+        <v>-0.8664413702415814</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9635242474916268</v>
+        <v>-0.9726857532940798</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.194982153547826</v>
+        <v>-1.203586600705108</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.926397593141985</v>
+        <v>-0.9431172052493935</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.13375025639251</v>
+        <v>-1.157403069054773</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.008374288999462</v>
+        <v>-1.032431662160356</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.8002069126336835</v>
+        <v>-0.8634245361237376</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.077768423449477</v>
+        <v>-1.147672863657633</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9599021909241898</v>
+        <v>-1.037492975005186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.1156</t>
+          <t>X &lt; 0.1154</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3353</v>
+        <v>3363</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.7280936894767152</v>
+        <v>-0.7032397869722828</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9568866704035273</v>
+        <v>-0.9673629841169173</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8602385499703402</v>
+        <v>-0.8415022984760938</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.189833021321505</v>
+        <v>-1.170069035618994</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7307499345173056</v>
+        <v>-0.7242093171932353</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5362726058690299</v>
+        <v>-0.5243629313672216</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3965599617773492</v>
+        <v>-0.3909391263648061</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5795304470985627</v>
+        <v>-0.5735295823723305</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4753637613211055</v>
+        <v>-0.4755477479977017</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7132078000440245</v>
+        <v>-0.7188412767811911</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6630379702100342</v>
+        <v>-0.6688991172934919</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5524744506319976</v>
+        <v>-0.5645225321279881</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.8367642149771939</v>
+        <v>-0.8539901056309063</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.7136787426545155</v>
+        <v>-0.7370748784505281</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1326</t>
+          <t>X &lt; 0.1324</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3501</v>
+        <v>3508</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3750537653095378</v>
+        <v>-0.3658346309080045</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5481226189013455</v>
+        <v>-0.54215254640647</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4720671302210988</v>
+        <v>-0.4659981970219391</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7536862457104618</v>
+        <v>-0.7187119304799907</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5074735303961617</v>
+        <v>-0.5103101101220702</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4225852618361827</v>
+        <v>-0.4496019286501394</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2638021836375799</v>
+        <v>-0.2672639909764172</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4302097290314393</v>
+        <v>-0.4330492275756086</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3614944716459902</v>
+        <v>-0.3690633835096335</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6822124603934938</v>
+        <v>-0.6647689561940666</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8425705731674569</v>
+        <v>-0.8246780942563205</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7352770983944268</v>
+        <v>-0.7507448728822794</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.082470987187094</v>
+        <v>-1.101629181504769</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.8938042741718277</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.1497</t>
+          <t>X &lt; 0.1494</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3601</v>
+        <v>3611</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3503128207944499</v>
+        <v>-0.3302001251077371</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.286400490606205</v>
+        <v>-0.2980915597806231</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1956221240785752</v>
+        <v>-0.2076232539621756</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5488388937042075</v>
+        <v>-0.5598492918294085</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2411983056721851</v>
+        <v>-0.260756638978755</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1226400866183752</v>
+        <v>-0.111047761397991</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2199682607953974</v>
+        <v>-0.2395693678379658</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4224230132634048</v>
+        <v>-0.4138912923903248</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2741076323824103</v>
+        <v>-0.2698113008533127</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5540025126469601</v>
+        <v>-0.5528743888226018</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7433023830793246</v>
+        <v>-0.7416833415800568</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6102504470383749</v>
+        <v>-0.6128209624701313</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9871974368306908</v>
+        <v>-0.9926150880188516</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8570842469577968</v>
+        <v>-0.8666637144921197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.1667</t>
+          <t>X &lt; 0.1664</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3695</v>
+        <v>3705</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.215543862249568</v>
+        <v>-0.22393646178854</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2749993450710662</v>
+        <v>-0.2864554421924268</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2235167895188965</v>
+        <v>-0.2351431523941372</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.429522858691989</v>
+        <v>-0.4405883483945487</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06232452693182466</v>
+        <v>-0.08064078646311401</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0338160739673512</v>
+        <v>0.01836766562045256</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.03613702436899757</v>
+        <v>-0.0545211891909716</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1912234640965309</v>
+        <v>-0.2092303329266869</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1832980207741173</v>
+        <v>-0.2044533827653865</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3424822869533912</v>
+        <v>-0.3663966536436618</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5050748022830405</v>
+        <v>-0.5285752619496549</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3474183512530828</v>
+        <v>-0.3744720633750447</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6712804739120486</v>
+        <v>-0.7006250255120889</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.6739671681430579</v>
+        <v>-0.706424589102653</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1837</t>
+          <t>X &lt; 0.1835</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3771</v>
+        <v>3781</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2081887578070791</v>
+        <v>-0.2170174653719599</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2195142303917308</v>
+        <v>-0.2309108451865285</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2034255971950998</v>
+        <v>-0.2148749996233619</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3762199066849803</v>
+        <v>-0.3872140784565019</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.212398235320876</v>
+        <v>-0.2289777500736676</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.0328642322318089</v>
+        <v>-0.04734625230304346</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07666281287013987</v>
+        <v>-0.06720871422465535</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.07918138743934833</v>
+        <v>-0.06972828373018558</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.04613013254690657</v>
+        <v>-0.03933946469867777</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2456743077071692</v>
+        <v>-0.2409493589949605</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4355862318559574</v>
+        <v>-0.4303646619327779</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2008822489227029</v>
+        <v>-0.2252947598032975</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4206010543567089</v>
+        <v>-0.4470307996751046</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3920995285934481</v>
+        <v>-0.4211927619506923</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.2007</t>
+          <t>X &lt; 0.2005</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3848</v>
+        <v>3859</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.05926360888193472</v>
+        <v>-0.05659942819276864</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.05065134639610847</v>
+        <v>-0.0504059340676335</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.09454388928092072</v>
+        <v>-0.09426204047640141</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2353419884040449</v>
+        <v>-0.2346305800686892</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.007719872747770751</v>
+        <v>-0.01185218423749745</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1223531242226699</v>
+        <v>0.1199544206465717</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.337849033930752e-05</v>
+        <v>-0.004153929080722207</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.0141236370039266</v>
+        <v>0.009865861283522293</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.04531990418431064</v>
+        <v>0.03891549883154966</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.0893196489077468</v>
+        <v>-0.09757785458585033</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2015848362006025</v>
+        <v>-0.2095734759530501</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.0227746422436681</v>
+        <v>-0.03331415545155636</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.09057221101362245</v>
+        <v>-0.1030644250015058</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1100132381539396</v>
+        <v>-0.1244525861189274</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.2178</t>
+          <t>X &lt; 0.2175</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3896</v>
+        <v>3906</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.01225396862594152</v>
+        <v>-0.02223226377445542</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.04911338255417519</v>
+        <v>-0.0350959544532472</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.02053104610596534</v>
+        <v>-0.006557151101986847</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.004369818937924208</v>
+        <v>-0.01597840361885972</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1114641307950137</v>
+        <v>0.0961367375373996</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.141165619971261</v>
+        <v>0.1530159019198578</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.04485872714326433</v>
+        <v>0.05523398146035419</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.07874526863961506</v>
+        <v>0.08906622530757602</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.08318943566462877</v>
+        <v>0.09177379043674705</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.008961792848964478</v>
+        <v>-0.02739268251929872</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.01975392775667473</v>
+        <v>-0.03815029458946384</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.106016012970791</v>
+        <v>0.08555556423699073</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.08523302798251109</v>
+        <v>0.06311133764583587</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.01752308034746619</v>
+        <v>-0.006183498369196627</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.2348</t>
+          <t>X &lt; 0.2345</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3941</v>
+        <v>3951</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.00241324854142988</v>
+        <v>-0.01263452922604102</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.06929428419336858</v>
+        <v>0.05760687597785363</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.008128569081968351</v>
+        <v>-0.01958621183558051</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.09190526175296299</v>
+        <v>-0.103166588523834</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.06708739859514878</v>
+        <v>0.05259790089512251</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1504735896170288</v>
+        <v>0.1371790726311986</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1556183563584099</v>
+        <v>0.1408763905689199</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1584858394031556</v>
+        <v>0.1437762910294182</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1875462142363489</v>
+        <v>0.1713243774487125</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1121262445888931</v>
+        <v>0.09472927130262576</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1245073302659989</v>
+        <v>0.10709252275241</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1985480371058941</v>
+        <v>0.1794945572306617</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1985973651438684</v>
+        <v>0.1781337877483793</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1342668684707533</v>
+        <v>0.1124938008503875</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.2518</t>
+          <t>X &lt; 0.2515</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3986</v>
+        <v>3996</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1322372577877289</v>
+        <v>0.146410998759805</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.16002393943333</v>
+        <v>0.1731781558254255</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.05403217090622547</v>
+        <v>0.06750267488926909</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.02273101461452143</v>
+        <v>0.0113044718636246</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1738981271957698</v>
+        <v>0.1598501991586474</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1846093716643651</v>
+        <v>0.1716482659788952</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1637062183235471</v>
+        <v>0.1496494974492251</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2113785516074032</v>
+        <v>0.1972559954531761</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.214380539770886</v>
+        <v>0.1990980204889254</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1552950029867901</v>
+        <v>0.1391034811635734</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1903069404516202</v>
+        <v>0.1740478048202689</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.3391422773462764</v>
+        <v>0.3213438780459015</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3846472326928421</v>
+        <v>0.3656225824820822</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3236381174743315</v>
+        <v>0.3035732630004659</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2688</t>
+          <t>X &lt; 0.2685</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4029</v>
+        <v>4040</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.006893269524951506</v>
+        <v>-0.005794035595094726</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04607391275927597</v>
+        <v>-0.04590490214550158</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.05618043904628678</v>
+        <v>-0.05602220815759296</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06103063760467364</v>
+        <v>-0.06084656084656359</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.05800908560651408</v>
+        <v>0.05605305006525896</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1212867434317033</v>
+        <v>0.1200694100522099</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.07491108452025941</v>
+        <v>0.07292794298867733</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.09229279645396815</v>
+        <v>0.09021608980046381</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1193725228483373</v>
+        <v>0.116331320322189</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1262178469178394</v>
+        <v>0.1221895345760302</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1834676960214949</v>
+        <v>0.1792618216561621</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2814649038713455</v>
+        <v>0.2761084943966168</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3964286986358303</v>
+        <v>0.3898302953070356</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3633028811040973</v>
+        <v>0.355927597533011</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2859</t>
+          <t>X &lt; 0.2855</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4047</v>
+        <v>4057</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.0313992404016048</v>
+        <v>0.02060070582555085</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.009893441812018011</v>
+        <v>-0.001374434741777009</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05119090608609866</v>
+        <v>-0.06224813729559742</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.0554405757582046</v>
+        <v>-0.06651094172609362</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.08533821626173221</v>
+        <v>0.07244715586488581</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1496617591234894</v>
+        <v>0.1373406301952471</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1031228911368771</v>
+        <v>0.09014688031759022</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1183600448183455</v>
+        <v>0.1054178387254865</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1450550114288589</v>
+        <v>0.1312727808362482</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09872924893242896</v>
+        <v>0.08441251834651808</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1548080840285522</v>
+        <v>0.1403817528392963</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.227817936331121</v>
+        <v>0.2124202366242969</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.3403890160183067</v>
+        <v>0.3239945156951691</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3084006995335358</v>
+        <v>0.2912612220958763</v>
       </c>
     </row>
   </sheetData>
